--- a/public/data/halife_products.xlsx
+++ b/public/data/halife_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,75 +614,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BEST PHAGE TEST 01</t>
+          <t>NANO BẠC AG+</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
+          <t>Thuốc kháng sinh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Khoáng chất &amp; Vi sinh vật</t>
+          <t>Diệt khuẩn, virus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung khoáng chất, vi sinh vật có lợi cho gia súc gia cầm</t>
+          <t>Sát trùng thế hệ mới, diệt khuẩn mạnh, diệt sạch virus, vi khuẩn gây bệnh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xử lý hoàn toàn các vi khuẩn gây bệnh đặc hiệu như Salmonella spp., Escherichia coli và C.perfringens trên gia súc, gia cầm. Cải thiện sức khỏe đường ruột, sản sinh vi khuẩn có lợi, hấp thu thức ăn triệt để, cải thiện FCR. Sử dụng ở tất cả các giai đoạn của vật nuôi.</t>
+          <t>Tiêu diệt virus ASF, PRRS, H5N1, H7N9 gây bệnh heo châu Phi, cúm gia cầm, lở mồm long móng,... Diệt sạch vi khuẩn E.coli, Salmonella, Clostridium và nấm mốc gây bệnh đường ruột, hô hấp. Xử lý nước uống, ngăn nguồn nhiễm khuẩn từ nước.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sản sinh vi khuẩn có lợi;Điều trị viêm ruột;tiêu chảy E.coli;Duy trì tiêu hóa khỏe mạnh</t>
+          <t>Diệt khuẩn;Diệt virus;Sát trùng chuồng trại;nước uống</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Trộn đều vào thức ăn hoặc nước uống theo liều lượng hướng dẫn</t>
+          <t>Phòng dịch:
+ Khử trùng định kỳ: 5ml / 1 Lít nước sạch, phun 8-10 m2 nền chuồng, phun trực tiếp lên vật nuôi 1 lần/ tuần.
+ Khử trùng khi có nguy cơ dịch, áp lực mầm bệnh cao : Tăng liều lên gấp đôi
+ Xử lý khi có dịch: 5ml / 1 Lít nước sạch, phun 5-7 m2 nền chuồng, phun trực tiếp lên vật nuôi 1 -2 lần/ ngày đến khi hết dịch.
+ Khử khuẩn nước dàn lạnh: 0,5 Lit/ 1000 Lít nước sạch, bổ sung 2 tuần 1 lần để duy trì nồng độ diệt khuẩn.
+ Sát trùng bầu vú: 5ml / 1 Lít nước sạch phun lên bầu vú.
+ Sát trùng vết thương: Bôi trực tiếp NANO BẠC Ag+ , để khô tự nhiên, ngày 1-2 lần.
+ Khử trùng dụng cụ ngoại khoa: Phun xịt trực tiếp, để 30 phút hoặc pha loãng tỷ lệ 1 NANO BẠC Ag+/ 2 Nước sạch và ngâm trong 45 phút.
+ Khử trùng nước uống : 1ml / 1 lít nước uống. Sản phẩm hỗ trợ điều trị bệnh khi kết hợp cùng kháng sinh khi dùng 1-2ml/ Lít nước uống/ngày.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>489000</v>
+        <v>260000</v>
       </c>
       <c r="J2" t="n">
-        <v>520000</v>
+        <v>350000</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lọ</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1 lít</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Gia súc, Gia cầm</t>
+          <t>Chuồng trại, nước</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Vi sinh vật có lợi, khoáng chất</t>
+          <t>Trong 1000ml có chứa:
+Silver ( nitrate ) 100 mg
+Dung môi vừa đủ 1000ml</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2-3ml/1 lít nước hoặc 1kg thức ăn</t>
+          <t>Pha loãng theo tỉ lệ hướng dẫn trên nhãn sản phẩm</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -692,7 +702,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng</t>
+          <t>Trong bao bì kín, nơi khô ráo thoáng mát, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -710,62 +720,54 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>VN-2024-BPHAGE</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="b">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>/images/product-6fe759f3-1753194718.jpg</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>/images/product-a9e9eeec-1753024799.png;/images/product-0680793c-1753024799.png;/images/product-6aa5133d-1753184918.png</t>
-        </is>
-      </c>
+          <t>/images/product-83af55e3-1753245712.jpg</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>best phage,vi sinh vật,khoáng chất,gia súc,gia cầm,tiêu hóa,E.coli,Salmonella,FCR</t>
+          <t>adekol,sát trùng,diệt khuẩn,virus,chuồng trại,nước uống</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>best phage,vi sinh vật có lợi,khoáng chất gia súc</t>
+          <t>adekol,sát trùng chăn nuôi,diệt khuẩn heo cúm gia cầm</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>BEST PHAGE - Thức ăn bổ sung giúp cải thiện đường ruột, kháng khuẩn, tăng miễn dịch</t>
+          <t>ADEKOL - Sát trùng thế hệ mới, diệt sạch virus và vi khuẩn gây bệnh</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -776,75 +778,86 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOOST PHAGE</t>
+          <t>CANXI VITA D3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thảo dược</t>
+          <t>Thức ăn bổ sung</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tăng cường miễn dịch</t>
+          <t>Khoáng chất &amp; Vitamin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Thảo dược tự nhiên hỗ trợ tiêu hóa và miễn dịch cho gia súc, gia cầm</t>
+          <t>Bổ sung Canxi và Vitamin D3, tăng tỷ lệ đẻ vỏ dày, lông bóng</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thảo dược tự nhiên xử lý tiêu chảy, E.coli, phân xanh, phân vàng, phân trắng; tăng lực, kích thích tăng trưởng, tăng khả năng tiêu hóa, chống còi cọc, stress. Hỗ trợ điều trị vô sinh, tăng sản lượng trứng, phòng bệnh bại liệt, co giật,...</t>
+          <t>Cung cấp Canxi hữu cơ và Vitamin D3 giúp hấp thụ tốt hơn. Tăng sản lượng trứng, kéo dài thời gian khai thác, vỏ bóng, đều và chắc. Hỗ trợ phục hồi xương, tăng miễn dịch và sức đề kháng cho vật nuôi.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Xử lý tiêu chảy;Kích thích ăn uống;Tăng miễn dịch;Tăng trưởng và sinh sản</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1ml/2 lít nước đối với gia cầm, 1ml/1 lít nước hoặc 500gr thức ăn đối với gia súc</t>
-        </is>
-      </c>
+          <t>Bổ sung Canxi;Tăng chất lượng trứng;Phục hồi xương và miễn dịch</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>95000</v>
+        <v>145000</v>
       </c>
       <c r="J3" t="n">
-        <v>110000</v>
+        <v>230000</v>
       </c>
       <c r="K3" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Lọ</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1 lít</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Gia súc, Gia cầm</t>
+          <t>Gia cầm, gia súc</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Thảo dược thiên nhiên</t>
+          <t>Vitamin B1*min 2000mg
+Vitamin D3*min 1000000IU
+Vitamin B6*min 2000mg
+Sorbitol*min 5000mg
+Canxi*min - max 7,000.00 - 8,000.00mg
+Biotin*min 2000mg
+Vitamin C*min 1000mg
+Đồng*min - max 500.00 - 570.00mg
+Sắt*min - max 600.00 - 800.00mg
+Tá dược vừa đủ 1000g 
+Sản phẩm không chứa kháng sinh, hoocmon và các chất độc hại.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1ml/2 lít nước đối với gia cầm, 1ml/1 lít nước hoặc 500gr thức ăn đối với gia súc</t>
+          <t>Hòa vào nước uống hoặc trộn thức ăn, dùng liên tục trong 3-5 ngày. 
+- Gà, vịt, cút đẻ: 5ml/ 10 lít nước/ 40-50 con.
+- Gà, vịt, cút thịt: 5ml/20 ml nước/100 con.
+- Lợn nái: 20 ml/ nái/ ngày. 
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi. 
+Lưu ý: nên sử dụng kết hợp sản phẩm men sống và sản phẩm siêu úm gà vịt để đạt hiệu quả cao nhất.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -854,7 +867,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng</t>
+          <t xml:space="preserve">Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C. </t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -872,13 +885,9 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>VN-2024-BOOSTPHAGE</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
@@ -887,47 +896,43 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>/images/product-461807d2-1752511758.png</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>/images/boost-phage.png;/images/gallery-boost-phage.png</t>
-        </is>
-      </c>
+          <t>/images/product-785949d1-1753332079.jpg</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>boost phage,thảo dược,tiêu chảy,e.coli,miễn dịch</t>
+          <t>Canxi,trứng đẹp,lông bóng,vỏ trứng chắc,vitamin D3</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>boost phage,thảo dược tự nhiên,chống tiêu chảy,miễn dịch</t>
+          <t>canxi vita D3,canxi hữu cơ,vitamin D3,trứng dày,vỏ bóng</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>BOOST PHAGE - Thảo dược tự nhiên hỗ trợ tiêu hóa, tăng trưởng và miễn dịch</t>
+          <t>CANXI VITA D3 - Bổ sung canxi hữu cơ và vitamin giúp trứng dày, bóng, tăng miễn dịch</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -938,75 +943,76 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADEKOL</t>
+          <t>GLUCO KC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thuốc kháng sinh</t>
+          <t>Thức ăn bổ sung</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Diệt khuẩn, virus</t>
+          <t>Thải độc, hồi sức</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sát trùng thế hệ mới, diệt khuẩn mạnh, diệt sạch virus, vi khuẩn gây bệnh</t>
+          <t>Cầm máu, giải độc, thanh nhiệt, giảm stress, tăng đề kháng</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tiêu diệt virus ASF, PRRS, H5N1, H7N9 gây bệnh heo châu Phi, cúm gia cầm, lở mồm long móng,... Diệt sạch vi khuẩn E.coli, Salmonella, Clostridium và nấm mốc gây bệnh đường ruột, hô hấp. Xử lý nước uống, ngăn nguồn nhiễm khuẩn từ nước.</t>
+          <t xml:space="preserve">Cung cấp vitamin K3, C cho cơ thể gia súc, gia cầm, giúp giữ vững thành mạch, giúp cầm máu, tăng sức đề kháng cơ thể vật nuôi, giải nhiệt, tăng lực cho vật nuôi. </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diệt khuẩn;Diệt virus;Sát trùng chuồng trại;nước uống</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Pha loãng theo tỉ lệ hướng dẫn trên nhãn sản phẩm</t>
-        </is>
-      </c>
+          <t>Hỗ trợ cầm máu;Giải độc gan;Tăng miễn dịch</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>150000</v>
+        <v>99000</v>
       </c>
       <c r="J4" t="n">
-        <v>150000</v>
+        <v>99000</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1 lít</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Chuồng trại, nước</t>
+          <t>Gia súc, Gia cầm</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Hợp chất sát trùng</t>
+          <t>Vitamine K3 min 5000 mg
+Vitamin C min 30.000 mg
+Tá dược vừa đủ 1000 g</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pha loãng theo tỉ lệ hướng dẫn trên nhãn sản phẩm</t>
+          <t xml:space="preserve">Cách dùng: Pha nước uống hoặc  trộn vào thức ăn.
+Liều dùng:
+Gà, vịt, ngan, ngỗng: pha 3 g/ lít nước uống hoặc trộn 3 g/ kg thức ăn. 
+Lợn, trâu, bò: Pha 100 g/ 50 lít nước uống hoặc trộn 100 g/ 50-60 kg thức ăn. </t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1016,7 +1022,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng</t>
+          <t>Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1034,62 +1040,58 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>VN-2024-ADEKOL</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="b">
         <v>1</v>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>/images/product-3dc4520b-1752512992.png</t>
+          <t>/images/product-87f2e00a-1753328004.jpg</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>/images/adekol.png;/images/gallery-adekol.png</t>
+          <t>/images/gluco-kc.png;/images/gallery-gluco-kc.png</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>adekol,sát trùng,diệt khuẩn,virus,chuồng trại,nước uống</t>
+          <t>gluco kc,cầm máu,giải độc,tăng trọng,tăng đề kháng</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>adekol,sát trùng chăn nuôi,diệt khuẩn heo cúm gia cầm</t>
+          <t>gluco kc,giải độc,cầm máu,tăng miễn dịch</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>ADEKOL - Sát trùng thế hệ mới, diệt sạch virus và vi khuẩn gây bệnh</t>
+          <t>GLUCO KC - Tăng cường đề kháng, giải độc và hồi phục sức khỏe cho vật nuôi</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1100,75 +1102,75 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CANXI VITA D3</t>
+          <t>BROM-HEN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
+          <t>Thuốc kháng sinh</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Khoáng chất &amp; Vitamin</t>
+          <t>Điều trị hô hấp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bổ sung Canxi và Vitamin D3, tăng tỷ lệ đẻ vỏ dày, lông bóng</t>
+          <t>Giảm ho, long đờm, chống co thắt phế quản</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cung cấp Canxi hữu cơ và Vitamin D3 giúp hấp thụ tốt hơn. Tăng sản lượng trứng, kéo dài thời gian khai thác, vỏ bóng, đều và chắc. Hỗ trợ phục hồi xương, tăng miễn dịch và sức đề kháng cho vật nuôi.</t>
+          <t xml:space="preserve">Trị bệnh phế quản phổi cấp và mãn tính liên quan đến tiết chất nhầy trên bê, lợn, gia cầm, chó, mèo.
+Giảm ho, tiêu đờm, chống co thắt phế quản trong các bệnh viêm phế quản, viêm thanh quản truyền nhiễm, viêm phổi, suyễn, sổ mũi truyền nhiễm, CRD, CCRD. </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bổ sung Canxi;Tăng chất lượng trứng;Phục hồi xương và miễn dịch</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Trộn 1ml/lít nước hoặc 1ml/1kg thức ăn dùng hàng ngày</t>
-        </is>
-      </c>
+          <t>Giảm ho;Long đờm;Giảm co thắt phế quản</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>145000</v>
+        <v>180000</v>
       </c>
       <c r="J5" t="n">
-        <v>145000</v>
+        <v>250000</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1 lít</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Gia cầm</t>
+          <t>Gia súc, Gia cầm</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Canxi hữu cơ, Vitamin D3</t>
+          <t>Bromhexin HCl 1 g
+Tá dược vừa đủ 100 g</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1ml/lít nước hoặc 1ml/1kg thức ăn</t>
+          <t>Pha nước uống hoặc trộn với thức ăn dùng liên tục 3 – 5 ngày theo liều:
+– Gà, vịt, ngan, cút: 1g/10 – 12 kg TT hoặc 1 g/1 -2 lít nước uống hoặc trộn 1 g/2 kg thức ăn.
+– Lợn và gia súc khác: 1 g/18 – 20 kg thể trọng.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1178,7 +1180,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Nơi khô ráo, thoáng mát</t>
+          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1196,62 +1198,54 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>VN-2024-CANXID3</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>/images/product-dd6698d5-1752511840.png</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>/images/canxi-vita-d3.png;/images/gallery-canxi-vita-d3.png</t>
-        </is>
-      </c>
+          <t>/images/product-f5e7a084-1753327157.jpg</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>canxi,trứng đẹp,lông bóng,vỏ trứng chắc,vitamin D3</t>
+          <t>brom-hen,giảm ho,long đờm,phế quản,hô hấp</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>canxi vita D3,canxi hữu cơ,vitamin D3,trứng dày,vỏ bóng</t>
+          <t>brom-hen,trị ho,trị đờm,vật nuôi viêm phế quản</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>CANXI VITA D3 - Bổ sung canxi hữu cơ và vitamin giúp trứng dày, bóng, tăng miễn dịch</t>
+          <t>BROM-HEN - Hỗ trợ điều trị ho, đờm và viêm phế quản hiệu quả</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1262,85 +1256,88 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GLUCO KC</t>
+          <t>ENDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
+          <t>Bộ sản phẩm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thải độc, hồi sức</t>
+          <t>Điều trị tiêu chảy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cầm máu, giải độc, thanh nhiệt, giảm stress, tăng đề kháng</t>
+          <t>Tiêm 1 mũi duy nhất, đặc trị tiêu chảy do nhiễm khuẩn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hỗ trợ đông máu trong tổn thương, stress, viêm gan, viêm túi mật. Đào thải độc tố, giảm mệt mỏi, tăng đề kháng, cải thiện dinh dưỡng, tăng trọng</t>
+          <t>Trị nhiễm trùng đường tiêu hóa, hô hấp, niệu sinh dục, nhiễm khuẩn huyết, nhiễm trùng da, vết thương trên trâu, bò, bê, nghé, dê, cừu, lợn.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hỗ trợ cầm máu;Giải độc gan;Tăng miễn dịch</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1g/1–2 lít nước uống hoặc 1g/1kg thức ăn dùng 3–5 ngày</t>
-        </is>
-      </c>
+          <t>Điều trị nhiễm khuẩn nặng;Tiêu chảy cấp;Phòng kế phát sau tiêu chảy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>99000</v>
+        <v>280000</v>
       </c>
       <c r="J6" t="n">
-        <v>99000</v>
+        <v>350000</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>Lọ tiêm</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Gia súc, Gia cầm</t>
+          <t>Gia súc</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Gluco-K, vitamin C</t>
+          <t>Trong 100ml có chứa:
+Enrofloxacin 10 g
+Dung môi vừa đủ 100 ml</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn</t>
+          <t>Tiêm mũi duy nhất, tiêm bắp hoặc tiêm dưới da
+- Gà, vịt, ngan, cút: 1ml/6-8kg TT.
+- Lợn: 1ml/8-12kg TT.
+- Lợn con: 1ml/6-7kg TT.
+- Trâu, bò, dê, cừu: 1ml/15-20kg TT.
+Trường hợp bệnh nặng: Tiêm nhắc lại sau 36-48h.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0 ngày</t>
+          <t>5 ngày</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Tránh ánh nắng trực tiếp</t>
+          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1358,13 +1355,9 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>VN-2024-GLUCOKC</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -1373,47 +1366,43 @@
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>/images/product-076e4305-1752511875.png</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>/images/gluco-kc.png;/images/gallery-gluco-kc.png</t>
-        </is>
-      </c>
+          <t>/images/product-edb21e58-1753327191.jpg</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>gluco kc,cầm máu,giải độc,tăng trọng,tăng đề kháng</t>
+          <t>endia,tiêu chảy,thuốc tiêm,viêm tử cung,nhiễm khuẩn</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>gluco kc,giải độc,cầm máu,tăng miễn dịch</t>
+          <t>endia,đặc trị tiêu chảy,thuốc tiêm nhiễm khuẩn,heo</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>GLUCO KC - Tăng cường đề kháng, giải độc và hồi phục sức khỏe cho vật nuôi</t>
+          <t>ENDIA - Khắc tinh tiêu chảy, hiệu quả cao với 1 mũi tiêm duy nhất</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1424,11 +1413,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADE TRỨNG</t>
+          <t>BV - BIOTIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1438,34 +1427,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tăng năng suất trứng</t>
+          <t>Tăng trưởng &amp; chất lượng trứng</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tăng trọng lượng, vỏ dày, màu đẹp, chống stress</t>
+          <t>Tăng trọng, mọc lông, chống cắn mổ, chống còi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tăng năng suất trứng, màu đỏ lòng đậm, vỏ dày đều. Ngừa sảy thai, tăng miễn dịch, giảm rụng lông, tăng tiêu hóa. Giúp gà đẻ lâu dài và ổn định</t>
+          <t>Kích thích mọc lông, chống cắn mổ
+Bổ sung vitamin thiết yếu và khoáng chất vi lượng cho gia cầm
+Vỗ béo, chống còi, tăng sản lượng thịt, tăng số lượng và chất lượng trứng. 
+Tạo màu vàng đẹp cho lòng đỏ trứng
+Nâng cao năng suất cho gia cầm sinh sản 
+Trứng to, vỏ dày, tỷ lệ đẻ cao, kéo dài.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tăng sản lượng trứng;Cải thiện vỏ và lòng trứng;Chống stress</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn trong suốt giai đoạn đẻ</t>
-        </is>
-      </c>
+          <t>Mọc lông;Chống còi;Tăng chất lượng trứng</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>175000</v>
+        <v>190000</v>
       </c>
       <c r="J7" t="n">
-        <v>175000</v>
+        <v>250000</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1482,17 +1472,30 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Gia cầm</t>
+          <t>Gia cầm, gia súc</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Vitamin A, D3, E, khoáng</t>
+          <t>Vitamin B1 (min) 10000mg 
+Vitamin B2(min) 3000 mg
+Vitamin B6(min) 300 mg
+Biotin (min) 450 mg
+Kẽm (min- max) 70-150 mg
+Lysine (min) 2000 mg
+Vitamin D3 (min) 2000 mg
+Canxi (min-max) 2000-3500mg 
+Tá dược vừa đủ 1000 g 
+Thành phần bổ sung hỗn hợp 10 lại enzyme hữu hiệu: Phytase, amylase, xylanase, protease, mannanase, cellulose, pectinase, B- Glucannsase, a- Galactosidase, lipase. 
+Sản phẩm không chứa chất kháng sinh, hoocmon và các chất độc hại.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn</t>
+          <t>Pha nước uống hoặc trộn thức ăn.
+Gà, vịt, lợn con: 100 g/ 50-100 kg thức ăn 
+Lợn nái, lợn con: 20g/20-30 kg thức ăn. 
+Trâu, bò, dê, cừu, bê, nghé: 20 g/ 50 kg thức ăn.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1502,7 +1505,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Để nơi khô mát, tránh ánh sáng</t>
+          <t>Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ c.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1520,62 +1523,54 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>VN-2024-ADETRUNG</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>/images/product-9b0f33c6-1752511898.png</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>/images/ade-trung.png;/images/gallery-ade-trung.png</t>
-        </is>
-      </c>
+          <t>/images/product-1cef78f3-1753327271.jpg</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>ade trứng,trứng đẹp,tăng đẻ,vỏ trứng đều,phòng sảy thai</t>
+          <t>biotin,tăng trọng,mọc lông,vỏ trứng đỏ,chống mổ</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ade trứng,tăng trứng,tăng năng suất,ngừa sảy thai</t>
+          <t>bv biotin,tăng sản lượng,chống cắn mổ,tăng chất lượng trứng</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>ADE TRỨNG - Tăng năng suất và chất lượng trứng, giảm stress, hỗ trợ sinh sản</t>
+          <t>BV-BIOTIN - Siêu tăng trọng, chống cắn mổ, tăng chất lượng trứng rõ rệt</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1586,48 +1581,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BROM-HEN</t>
+          <t>AN THAI BỔ NÁI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thuốc kháng sinh</t>
+          <t>Thức ăn bổ sung</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Điều trị hô hấp</t>
+          <t>Hỗ trợ sinh sản</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Giảm ho, long đờm, chống co thắt phế quản</t>
+          <t>Tăng lượng sữa, dưỡng nái, ngừa sảy thai, thai khỏe, con sai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trị bệnh phế quản phổi cấp và mãn tính liên quan đến chất nhầy trên bê, lợn, gà, chó, mèo. Giảm ho, giảm đờm, chống co thắt trong các bệnh viêm phế quản và thanh phế quản truyền nhiễm.</t>
+          <t>Bổ sung probiotic,acid amin, hỗn hợp vitamin và khoáng thiết yếu cho vật nuôi, công thức đặc biệt bổ sung dưỡng chất cho đối tượng con nái để: 
+* Tăng cường sức khỏe, Tăng tỷ lệ đậu thai và tỷ lệ đẻ, Tăng số con trong lứa.
+* Đối với nái chửa: Cân bằng dinh dưỡng, bào thai phát triển tốt hơn, đẻ dễ dàng hơn.
+* Đối với nái chờ phối: Sử dụng sản phẩm thường xuyên giúp rút ngắn thời gian lên giống sau cai sữa, động dục mạnh hơn.
+* Phòng nứt móng, sừng hóa da.
+* Khung xương phát triển mạnh, hạn chế bại liệt.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Giảm ho;Long đờm;Giảm co thắt phế quản</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Trộn 1g/1-2 lít nước hoặc 1g/1kg thức ăn, dùng 3-5 ngày tùy mức độ bệnh</t>
-        </is>
-      </c>
+          <t>Bổ sung khoáng &amp; vitamin sinh sản;Ngừa sảy thai;Dưỡng nái</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>150000</v>
+        <v>220000</v>
       </c>
       <c r="J8" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1644,17 +1640,36 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Gia súc, Gia cầm, Chó, Mèo</t>
+          <t>Heo nái</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Bromhexin, thảo dược</t>
+          <t>Trong 1000g có chứa:
+Zn (Min - max) 1600 -1800 mg/kg
+Fe (Min - max) 3000 - 5000 mg/kg
+Lysine (min) 15000 mg/kg
+Vitamin A (min) 2.500.000 IU/kg
+Vitamin D (min) 1.000.000 IU/kg
+Vitamin E (min) 620 mg/kg
+Biotin (min) 400 mg/kg
+Senlen (min - max) 38-54 mg/kg
+Tá dược vừa đủ 1000g
+Thành phần nguyên liệu: 
+Bổ sung vi sinh vật có lợi: lactobacillus; sacharomyces; bacillus subtilis
+Bổ sung hỗn hợp 10 loại enzyme : Bổ sung hỗn hợp 10 enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)
+Bổ sung thành phần thảo dược: Mộc hương, hoài sơn, ý dĩ, thần khúc, sơn tra.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1g/1-2 lít nước hoặc 1g/1kg thức ăn</t>
+          <t>CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.
+LIỀU DÙNG: 
+Nái chửa : 1kg trộn với 400 – 600 kg thức ăn hỗn hợp.
+Nái hậu bị và nái chờ phối : 1kg trộn với 1.000 kg thức ăn hỗn hợp.
+Hòa nước: 1g/2-3 lít nước uống.
+Lưu ý : Có thể dùng chung với kháng sinh để phòng bệnh.
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1664,7 +1679,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Tránh ẩm, kín gió</t>
+          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1682,13 +1697,9 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>VN-2024-BROMHEN</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
@@ -1697,47 +1708,43 @@
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>/images/product-28f2b635-1752511921.png</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>/images/brom-hen.png;/images/gallery-brom-hen.png</t>
-        </is>
-      </c>
+          <t>/images/product-99896a92-1753321132.jpg</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>brom-hen,giảm ho,long đờm,phế quản,hô hấp</t>
+          <t>an thai bổ nái,dưỡng nái,tăng sữa,tăng đậu thai,sinh sản</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>brom-hen,trị ho,trị đờm,vật nuôi viêm phế quản</t>
+          <t>an thai bổ nái,dưỡng nái,ngừa sảy thai,vitamin sinh sản</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>BROM-HEN - Hỗ trợ điều trị ho, đờm và viêm phế quản hiệu quả</t>
+          <t>AN THAI BỔ NÁI - Dưỡng nái, bổ sung khoáng chất và vitamin giúp mẹ khỏe, con sai, ngừa sảy thai</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1748,85 +1755,85 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENDIA</t>
+          <t>ADE ĐẠM SỮA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bộ sản phẩm</t>
+          <t>Thức ăn bổ sung</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Điều trị tiêu chảy</t>
+          <t>Tăng trọng &amp; sức đề kháng</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tiêm duy nhất, đặc trị tiêu chảy do nhiễm khuẩn</t>
+          <t>Tăng trọng, tăng cơ, bung lông, giảm chi phí nuôi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Đặc trị nhiễm khuẩn nặng, ức chế enzym gyrase, diệt vi khuẩn. Hiệu quả với bệnh kế phát như viêm phổi, tụ huyết trùng, viêm tử cung.</t>
+          <t>Bổ sung vitamin, acid amin, enzyme và protein giúp vật nuôi tăng trưởng nhanh, hạn chế dùng kháng sinh, phục hồi sau mất sữa, tăng đề kháng, tiêu hóa tốt, xuất chuồng sớm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Điều trị nhiễm khuẩn nặng;Tiêu chảy cấp;Phòng kế phát sau tiêu chảy</t>
+          <t>Tăng trọng;Tăng cơ;Hạn chế kháng sinh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tiêm 1ml/10–15kg thể trọng, tiêm duy nhất 1 lần hoặc theo hướng dẫn bác sĩ thú y</t>
+          <t>1g/1kg thức ăn, dùng trong các giai đoạn cần tăng trưởng nhanh hoặc sau cai sữa</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>280000</v>
       </c>
       <c r="J9" t="n">
-        <v>280000</v>
+        <v>350000</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Lọ tiêm</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gia súc</t>
+          <t>Gia súc, Gia cầm</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Kháng sinh nhóm fluoroquinolone</t>
+          <t>Vitamin A, D, E, protein sữa</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1ml/10–15kg thể trọng</t>
+          <t>1g/1kg thức ăn</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5 ngày</t>
+          <t>0 ngày</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Nơi thoáng mát, tránh ánh nắng</t>
+          <t>Để nơi thoáng mát</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1846,7 +1853,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>VN-2024-ENDIA</t>
+          <t>VN-2024-ADESUA</t>
         </is>
       </c>
       <c r="W9" t="b">
@@ -1859,47 +1866,47 @@
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>/images/product-ef9509be-1752511939.png</t>
+          <t>/images/product-d9255d53-1753328021.jpg</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>/images/endia.png;/images/gallery-endia.png</t>
+          <t>/images/ade-dam-sua.png;/images/gallery-ade-dam-sua.png</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>endia,tiêu chảy,thuốc tiêm,viêm tử cung,nhiễm khuẩn</t>
+          <t>đạm sữa,tăng trọng,tăng cơ,vật nuôi lớn nhanh</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>endia,đặc trị tiêu chảy,thuốc tiêm nhiễm khuẩn,heo</t>
+          <t>ade đạm sữa,tăng cân,tăng cơ,protein,không kháng sinh</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>ENDIA - Khắc tinh tiêu chảy, hiệu quả cao với 1 mũi tiêm duy nhất</t>
+          <t>ADE ĐẠM SỮA - Tăng trọng, đạm cao, tăng cơ nhanh, giảm tiêu tốn thức ăn</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1910,11 +1917,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PIG PHAGE</t>
+          <t>OCTA-NEW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1924,41 +1931,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phage trị tiêu chảy</t>
+          <t>Viêm tử cung &amp; sinh dục</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Khắc tinh tiêu chảy cho heo con</t>
+          <t>Đặc trị viêm tử cung, viêm vú, mất sữa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xử lý vi khuẩn đặc hiệu gây tiêu chảy, bảo vệ sức khỏe đường ruột cho heo. Ngăn ngừa tái phát, tăng hấp thu, giảm chết sơ sinh.</t>
+          <t>Trị viêm tử cung trước và sau sinh, viêm vú, mất sữa ở gia súc. Trị viêm phổi, CRD, CCRD, bệnh tiêu hóa.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trị tiêu chảy;Tăng sức đề kháng ruột;Ngăn tái phát</t>
+          <t>Viêm tử cung;Mất sữa;Viêm phổi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Xịt trực tiếp 1–2ml vào miệng heo 1–2 lần/ngày trong 3–5 ngày hoặc theo hướng dẫn</t>
+          <t>Tiêm 1ml/10-15kg thể trọng trong 3-5 ngày hoặc theo chỉ định</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="J10" t="n">
-        <v>160000</v>
+        <v>320000</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Lọ xịt</t>
+          <t>Lọ tiêm</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1968,27 +1975,27 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Heo con</t>
+          <t>Gia súc</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Phage đặc hiệu E.coli</t>
+          <t>Oxytetracycline, multivitamin</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1–2ml/ngày</t>
+          <t>1ml/10-15kg thể trọng</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0 ngày</t>
+          <t>7 ngày</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Nơi khô ráo</t>
+          <t>Nơi mát, tránh ánh nắng</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2008,60 +2015,60 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>VN-2024-PIGPHAGE</t>
+          <t>VN-2024-OCTANEW</t>
         </is>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>/images/product-b56a2133-1752511961.png</t>
+          <t>/images/product-29a966ac-1753332407.jpg</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>/images/pig-phage.png;/images/gallery-pig-phage.png</t>
+          <t>/images/octa-new.png;/images/gallery-octa-new.png</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>pig phage,tiêu chảy heo con,xịt trị tiêu chảy,đường ruột khỏe</t>
+          <t>octa-new,viêm tử cung,mất sữa,sinh dục,crd</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>pig phage,phage tiêu chảy,heo con,kháng khuẩn đặc hiệu</t>
+          <t>octa-new,đặc trị viêm tử cung,sản khoa,mất sữa</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>PIG PHAGE - Phage xịt điều trị tiêu chảy đặc hiệu cho heo con</t>
+          <t>OCTA-NEW - Thuốc tiêm trị viêm tử cung, mất sữa và viêm hô hấp</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2072,11 +2079,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV - BIOTIN</t>
+          <t>WINTOSAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2086,61 +2093,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tăng trưởng &amp; chất lượng trứng</t>
+          <t>Hồi sức &amp; trao đổi chất</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tăng trọng, mọc lông, chống cắn mổ, chống còi</t>
+          <t>Tăng trao đổi chất, hồi sức, chống suy nhược</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kích thích mọc lông, chống cắn mổ. Tăng sản lượng thịt, duy trì tỉ lệ đẻ, vỏ trứng đỏ đều, đẹp, không biến dạng.</t>
+          <t>Giúp gia súc non phát triển, tăng sinh sản, giảm suy nhược, thiếu máu, tăng chuyển hóa.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mọc lông;Chống còi;Tăng chất lượng trứng</t>
+          <t>Hồi sức;Tăng trao đổi chất;Chống suy nhược</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn liên tục 5–7 ngày/lần</t>
+          <t>Tiêm 1ml/10kg thể trọng trong 3 ngày liên tiếp hoặc theo hướng dẫn</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>190000</v>
+        <v>320000</v>
       </c>
       <c r="J11" t="n">
-        <v>190000</v>
+        <v>400000</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>Lọ tiêm</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Gia cầm</t>
+          <t>Gia súc</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Biotin, vitamin nhóm B</t>
+          <t>Vitamin B-complex, Glucose, Electrolytes</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn</t>
+          <t>1ml/10kg thể trọng</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2150,7 +2157,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Khô mát, kín gió</t>
+          <t>Nơi mát, kín nắp</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2170,60 +2177,60 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>VN-2024-BVBIOTIN</t>
+          <t>VN-2024-WINTOSAL</t>
         </is>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>/images/product-21d78fe9-1752511977.png</t>
+          <t>/images/product-214a5212-1753332114.jpg</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>/images/bv-biotin.png;/images/gallery-bv-biotin.png</t>
+          <t>/images/wintosal.png;/images/gallery-wintosal.png</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>biotin,tăng trọng,mọc lông,vỏ trứng đỏ,chống mổ</t>
+          <t>wintosal,hồi sức,tăng trao đổi chất,giảm suy nhược,sinh sản</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>bv biotin,tăng sản lượng,chống cắn mổ,tăng chất lượng trứng</t>
+          <t>wintosal,tăng trao đổi chất,chống stress,thúc đẻ</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>BV-BIOTIN - Siêu tăng trọng, chống cắn mổ, tăng chất lượng trứng rõ rệt</t>
+          <t>WINTOSAL - Bổ trợ chuyển hóa, sinh sản, hồi sức nhanh chóng</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2234,11 +2241,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WINDOXCIN</t>
+          <t>GOOD SET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2248,46 +2255,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Điều trị hô hấp &amp; nhiễm khuẩn</t>
+          <t>Cử lý tối ưu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Điều trị viêm phổi, hen gà, CRD, tụ huyết trùng</t>
+          <t>Xử lý tối ưu hô hấp, viêm phổi trên vật nuôi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Điều trị các bệnh đường hô hấp như viêm phổi, tiêu chảy, viêm khớp, tử cung, tụ huyết trùng trên trâu, bò, lợn, gia cầm. Hiệu quả cao với bệnh mạn tính, CRD ghép E.coli.</t>
+          <t>Công thức, tá dược, dung môi dung hòa đặc biệt, giúp bộ đôi sản phẩm tiêu diệt hầy hết các loại vi khuẩn gây ra bệnh đường hô hấp cho gia súc:
+* Heo:
+- Phòng và trị bệnh viêm đường hô hấp phức hợp (heo hắt hơi từng hồi, chảy nước mũi, ho, khó thở, thở nhanh và nhiều, heo há hốc mồm để thở)
+- Phòng và trị bệnh viêm phổi, suyễn, tụ huyết trùng, viêm phổi - màng hổi, bệnh Glaser, viêm teo xoang mũi
+- Phòng các bệnh bội nhiễm và kế phát khi heo bệnh tai xanh (PRRS) và lở mồm long móng (FMD)
+* Trâu bò, dê, cừu:
+- Trị các bệnh đường hô hấp như viêm phổi, tụ huyết trùng, viêm hô hấp phức hợp, 
+- Viêm kết giác mạc,
+- Phòng các bệnh bội nhiễm và kế phát khi trâu bò, dê, cừu bệnh lở mồm long móng. bệnh thối móng"</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trị viêm phổi;Điều trị CRD;Hỗ trợ miễn dịch đường hô hấp</t>
+          <t>Phòng và trị viêm đường hô hấp;Phòng bệnh kế phát;Tối ưu phổi và miễn dịch</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn dùng trong 3–5 ngày</t>
+          <t>Tiêm bắp hoặc tiêm dưới da một liều duy nhất</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>950000</v>
+        <v>550000</v>
       </c>
       <c r="J12" t="n">
-        <v>950000</v>
+        <v>550000</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>2 chai</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2297,12 +2312,15 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Doxycycline, Enrofloxacin</t>
+          <t>WINFLO LA, ANPHA NEW</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1g/1–2 lít nước hoặc 1g/1kg thức ăn</t>
+          <t>Lấy 1ml ANPHA NEW + 1ml WINFLO LA lắc đều. Sau đó lấy 2 ml hỗn hợp dung dịch kháng sinh tiêm cho:
+- HEO: 2ml/15-20 kg thể trọng đối với bệnh nặng và 2ml/25-30 kg thể trọng đối với bệnh nhẹ. Tiêm bắp 1 liều duy nhất
+- TRÂU BÒ: 20ml/40kg thể trọng
+- DÊ, CỪU: 2ml /40 kg thể trọng</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2312,7 +2330,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Nơi khô, kín, tránh ánh sáng</t>
+          <t>Khô thoáng, tránh ánh nắng</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2332,7 +2350,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>VN-2024-WINDOXCIN</t>
+          <t>VN-2024-GOODSET</t>
         </is>
       </c>
       <c r="W12" t="b">
@@ -2345,47 +2363,47 @@
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>/images/product-e55af08f-1752512000.png</t>
+          <t>/images/product-d23b9ee5-1753321141.jpg</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>/images/windoxcin.png;/images/gallery-windoxcin.png</t>
+          <t>/images/product-bad4093e-1752512778.png;/images/product-ce5b7ccf-1752512778.png;/images/product-955251ab-1752512778.png</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>windoxcin,hô hấp,viêm phổi,CRD,E.coli,tụ huyết trùng</t>
+          <t>good set,hô hấp,viêm phổi,heo tai xanh,lở mồm long móng</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>windoxcin,trị viêm phổi,crd,hen gà,viêm tử cung</t>
+          <t>good set,viêm phổi,hô hấp,halife</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>WINDOXCIN - Đặc trị viêm phổi, tụ huyết trùng, CRD, hen gà, trên mọi loại vật nuôi</t>
+          <t>GOOD SET - Bộ đôi xử lý tối ưu các bệnh viêm phổi, hô hấp, phòng bệnh kế phát</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2396,85 +2414,73 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AN THAI BỔ NÁI</t>
+          <t>Cefket 1015</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Hỗ trợ sinh sản</t>
-        </is>
-      </c>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tăng lượng sữa, dưỡng nái, ngừa sảy thai, thai khỏe, con sai</t>
+          <t>Đặc trị viêm vú, viêm tử cung, viêm khớp, viêm móng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bổ sung Kẽm, Selen, Vitamin A-E bảo vệ niêm mạc tử cung, tăng đậu thai, giảm sảy thai, chết lưu. Cung cấp oxy, ngừa stress sinh sản. Con sinh ra khỏe mạnh, đồng đều.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Bổ sung khoáng &amp; vitamin sinh sản;Ngừa sảy thai;Dưỡng nái</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Trộn 10–20g/1kg thức ăn hoặc theo chỉ định bác sĩ thú y</t>
-        </is>
-      </c>
+          <t>ĐẶC TRỊ VIÊM VÚ, VIÊM TỬ CUNG, VIÊM MÓNG, VIÊM KHỚP, VIÊM PHỔI, PHỔI DÍNH SƯỜN, SỐT, BỎ ĂN KHÔNG RÕ NGUYÊN NHÂN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>220000</v>
+        <v>480000</v>
       </c>
       <c r="J13" t="n">
-        <v>220000</v>
+        <v>550000</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>hộp</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Heo nái</t>
+          <t>Gia súc, gia cầm</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Vitamin A, E, Selen, Kẽm</t>
+          <t>Ceftiofur (dạng hydroclorid).……5g
+Ketoprofen…………………...….....15g
+Dung môi vừa đủ……………...100ml</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10–20g/1kg thức ăn</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
+          <t>Tiêm bắp 1 liều duy nhất. Lắc kĩ trước khi sử dụng.
+Lấy 1ml/ 50 kg thể trọng mỗi lần tiêm. Dùng từ 3-5 ngày liên tục.
+Không tiêm quá 16 ml tại bất kì vị trí tiêm bắp nào. Các lần tiếp theo phải được tiêm ở vị trí khác.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Khô mát, kín, tránh ẩm</t>
+          <t>Trong bao bì kín, nơi khô ráo thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2484,7 +2490,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Halife</t>
+          <t>HALIFE Việt Nhật</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2494,60 +2500,44 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>VN-2024-ANTHAI</t>
+          <t>WIN-136</t>
         </is>
       </c>
       <c r="W13" t="b">
         <v>1</v>
       </c>
       <c r="X13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>/images/product-2fd9ea2b-1752512031.png</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>/images/an-thai.png;/images/gallery-an-thai.png</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>an thai bổ nái,dưỡng nái,tăng sữa,tăng đậu thai,sinh sản</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>an thai bổ nái,dưỡng nái,ngừa sảy thai,vitamin sinh sản</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>AN THAI BỔ NÁI - Dưỡng nái, bổ sung khoáng chất và vitamin giúp mẹ khỏe, con sai, ngừa sảy thai</t>
-        </is>
-      </c>
+          <t>/images/product-cf73eee0-1753322027.jpg</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2558,87 +2548,55 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ADE ĐẠM SỮA</t>
+          <t>ENDIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Tăng trọng &amp; sức đề kháng</t>
-        </is>
-      </c>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tăng trọng, tăng cơ, bung lông, giảm chi phí nuôi</t>
+          <t>KHẮC TINH TIÊU CHẢY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bổ sung vitamin, acid amin, enzyme và protein giúp vật nuôi tăng trưởng nhanh, hạn chế dùng kháng sinh, phục hồi sau mất sữa, tăng đề kháng, tiêu hóa tốt, xuất chuồng sớm</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tăng trọng;Tăng cơ;Hạn chế kháng sinh</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1g/1kg thức ăn, dùng trong các giai đoạn cần tăng trưởng nhanh hoặc sau cai sữa</t>
-        </is>
-      </c>
+          <t>KHẮC TINH TIÊU CHẢY</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>280000</v>
       </c>
       <c r="J14" t="n">
-        <v>280000</v>
+        <v>350000</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>hộp</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Vitamin A, D, E, protein sữa</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1g/1kg thức ăn</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Để nơi thoáng mát</t>
-        </is>
-      </c>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>24 tháng</t>
@@ -2646,7 +2604,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Halife</t>
+          <t>HALIFE Việt Nhật</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2654,62 +2612,42 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>VN-2024-ADESUA</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>/images/product-10aeb826-1752512040.png</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>/images/ade-dam-sua.png;/images/gallery-ade-dam-sua.png</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>đạm sữa,tăng trọng,tăng cơ,vật nuôi lớn nhanh</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>ade đạm sữa,tăng cân,tăng cơ,protein,không kháng sinh</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>ADE ĐẠM SỮA - Tăng trọng, đạm cao, tăng cơ nhanh, giảm tiêu tốn thức ăn</t>
-        </is>
-      </c>
+          <t>/images/product-4d1df8d6-1753332777.jpg</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2720,85 +2658,73 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OCTA-NEW</t>
+          <t>GLUCAN MAX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Viêm tử cung &amp; sinh dục</t>
-        </is>
-      </c>
+          <t>Vitamin &amp; khoáng chất</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Đặc trị viêm tử cung, viêm vú, mất sữa</t>
+          <t>Siêu đề kháng, siêu miễn dịch, bảo vệ vật nuôi toàn diện</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trị viêm tử cung trước và sau sinh, viêm vú, mất sữa ở gia súc. Trị viêm phổi, CRD, CCRD, bệnh tiêu hóa.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Viêm tử cung;Mất sữa;Viêm phổi</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Tiêm 1ml/10-15kg thể trọng trong 3-5 ngày hoặc theo chỉ định</t>
-        </is>
-      </c>
+          <t>Siêu đề kháng, siêu miễn dịch, bảo vệ vật nuôi toàn diện</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>320000</v>
+        <v>450000</v>
       </c>
       <c r="J15" t="n">
-        <v>320000</v>
+        <v>480000</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Lọ tiêm</t>
+          <t>hộp</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>100ml</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Gia súc</t>
-        </is>
-      </c>
+          <t>1KG</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Oxytetracycline, multivitamin</t>
+          <t>Trong 1000g có chứa:
+Beta-glucan tổng số* min.....................................10000mg
+Vitamin C* min......................................................... 20000mg
+Methionine* min..........................................................6000mg
+Lysine tổng số* min…...............................................20000mg
+Tá dược vừa đủ...............................................................1000g 
+Sản phẩm không chứa kháng sinh, hoocmon.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1ml/10-15kg thể trọng</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>7 ngày</t>
-        </is>
-      </c>
+          <t>Trộn vào thức ăn hoặc pha vào nước uống:
+Hoà 1g/2-3 lít nước hoặc 1g/10-20kg thể trọng/ ngày 
+Trộn thức ăn: 1-2kg/1000kg thức ăn.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Nơi mát, tránh ánh nắng</t>
+          <t>Trong bao bì khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2808,7 +2734,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Halife</t>
+          <t>HALIFE Việt Nhật</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2816,11 +2742,7 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>VN-2024-OCTANEW</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="b">
         <v>0</v>
       </c>
@@ -2831,47 +2753,31 @@
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>/images/product-b3e69e7d-1752512608.png</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>/images/octa-new.png;/images/gallery-octa-new.png</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>octa-new,viêm tử cung,mất sữa,sinh dục,crd</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>octa-new,đặc trị viêm tử cung,sản khoa,mất sữa</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>OCTA-NEW - Thuốc tiêm trị viêm tử cung, mất sữa và viêm hô hấp</t>
-        </is>
-      </c>
+          <t>/images/product-e50da535-1753340636.jpg</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2882,85 +2788,77 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMOXGENX</t>
+          <t>BEST PHAGE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nhiễm khuẩn tiêu hóa &amp; hô hấp</t>
-        </is>
-      </c>
+          <t>Bộ sản phẩm</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trị nhiễm trùng tiêu hóa, hô hấp và nhiễm khuẩn nội tạng</t>
+          <t>GIẢI PHÁP VÀNG THAY THẾ KHÁNG SINH
+CẢI THIỆN SỨC KHOẺ ĐƯỜNG RUỘT- NÂNG CAO KHẢ NĂNG MIỄN DỊCH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trị nhiễm trùng đường tiêu hóa, hô hấp, nhiễm nội tạng, viêm vú, tử cung và áp xe da trên trâu, bò, lợn.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Trị viêm ruột;Viêm tử cung;Áp xe</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Tiêm 1ml/10-15kg thể trọng, ngày 1-2 lần theo hướng dẫn bác sĩ thú y</t>
-        </is>
-      </c>
+          <t>Xử lí hoàn toàn các vi khuẩn gây bệnh như Salmonella spp, Escherichia coli và C.perfringens trên gia súc, gia cầm.
+Cải thiện sức khoẻ đường ruột, sản sinh vi khuẩn có lợi, hấp thu thức ăn triệt để, cải thiện FCR
+Sử dụng tất cả các giai đoạn của vật nuôi. 
+Kết hợp với sản phẩm Boost phage giúp tăng năng suất, hiệu quả chăn nuôi, sớm xuất bán</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>300000</v>
+        <v>489000</v>
       </c>
       <c r="J16" t="n">
-        <v>300000</v>
+        <v>550000</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Lọ tiêm</t>
+          <t>hộp</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>250ML</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Gia súc</t>
+          <t>Gia súc, gia cầm</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Amoxicillin, Gentamycin</t>
+          <t>Bacillus spp(min) 1x107
+Dung môi vừa đủ  1000ml</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1ml/10-15kg thể trọng</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>7 ngày</t>
-        </is>
-      </c>
+          <t>Lắc đều trước khi sử dụng. 
+Phòng bệnh: 1ml pha với 2 lít nước, dùng cho 30 kg thể trọng vật nuôi.
+Vật nuôi giai đoạn úm: Thay thế kháng sinh, dùng liên tục từ 5- 7 ngày khi bắt đầu giai đoạn úm. Sau đó, sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục từ 2-3 ngày.  
+Gia súc, gia cầm: Sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục 2-3 ngày.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Tránh ánh nắng trực tiếp</t>
+          <t>Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2970,7 +2868,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Halife</t>
+          <t>HALIFE Việt Nhật</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2978,11 +2876,7 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>VN-2024-AMOXGENX</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="b">
         <v>1</v>
       </c>
@@ -2993,1670 +2887,34 @@
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>/images/product-fa6c9e77-1752512649.png</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>/images/amoxgenx.png;/images/gallery-amoxgenx.png</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>amoxgenx,nhiễm trùng,viêm tử cung,áp xe,viêm hô hấp</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>amoxgenx,điều trị nhiễm khuẩn tiêu hóa,viêm tử cung,trâu bò lợn</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>AMOXGENX - Thuốc tiêm trị nhiễm khuẩn nội tạng, viêm tử cung, tiêu hóa, hô hấp</t>
-        </is>
-      </c>
+          <t>/images/product-e2bcbad7-1753437123.jpg</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WINTOSAL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hồi sức &amp; trao đổi chất</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Tăng trao đổi chất, hồi sức, chống suy nhược</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Giúp gia súc non phát triển, tăng sinh sản, giảm suy nhược, thiếu máu, tăng chuyển hóa.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hồi sức;Tăng trao đổi chất;Chống suy nhược</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Tiêm 1ml/10kg thể trọng trong 3 ngày liên tiếp hoặc theo hướng dẫn</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>250000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Lọ tiêm</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Gia súc</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Vitamin B-complex, Glucose, Electrolytes</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>1ml/10kg thể trọng</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Nơi mát, kín nắp</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>VN-2024-WINTOSAL</t>
-        </is>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>180</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>/images/product-00cbdb55-1752512709.png</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>/images/wintosal.png;/images/gallery-wintosal.png</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>wintosal,hồi sức,tăng trao đổi chất,giảm suy nhược,sinh sản</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>wintosal,tăng trao đổi chất,chống stress,thúc đẻ</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>WINTOSAL - Bổ trợ chuyển hóa, sinh sản, hồi sức nhanh chóng</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>2024-02-09</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GOOD SET</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Bộ sản phẩm</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cử lý tối ưu</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Cử lý tối ưu hô hấp, viêm phổi</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Phòng và trị bệnh viêm đường hô hấp phức hợp. Phòng và trị bệnh viêm phổi, hen, tụ huyết trùng, viêm teo xoang mũi. Phòng các bệnh bội nhiễm và kế phát (heo tai xanh, lở mồm long móng).</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Phòng và trị viêm đường hô hấp;Phòng bệnh kế phát;Tối ưu phổi và miễn dịch</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Theo hướng dẫn của bác sĩ thú y hoặc nhãn sản phẩm WINFLO LA và ANPHA NEW</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>550000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>550000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 chai</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>WINFLO LA, ANPHA NEW</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Dùng kết hợp 2 sản phẩm theo hướng dẫn</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>7 ngày</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Khô thoáng, tránh ánh nắng</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>VN-2024-GOODSET</t>
-        </is>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-      <c r="X18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>/images/product-7aadbcb7-1752512755.png</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>/images/product-bad4093e-1752512778.png;/images/product-ce5b7ccf-1752512778.png;/images/product-955251ab-1752512778.png</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>good set,hô hấp,viêm phổi,heo tai xanh,lở mồm long móng</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>good set,viêm phổi,hô hấp,halife</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>GOOD SET - Bộ đôi xử lý tối ưu các bệnh viêm phổi, hô hấp, phòng bệnh kế phát</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BEST PHAGE</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bộ sản phẩm</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Vi sinh vật &amp; Thảo dược</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Kháng sinh tự nhiên cho gia súc gia cầm</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Kết hợp BEST PHAGE và BOOST PHAGE giúp xử lý vi khuẩn gây bệnh (E.coli, Salmonella, Clostridium), cải thiện hệ tiêu hóa, miễn dịch và tăng trưởng.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Tiêu diệt vi khuẩn;Cải thiện miễn dịch;Tăng hấp thu;Kháng sinh tự nhiên</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kết hợp liều dùng theo từng lọ BEST PHAGE và BOOST PHAGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>489000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>489000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 lọ</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>BEST PHAGE, BOOST PHAGE</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Dùng kết hợp theo hướng dẫn</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Khô mát</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>VN-2024-BESTCOMBO</t>
-        </is>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-      <c r="X19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>/images/product-e99cff39-1752512826.png</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>/images/product-6a68e21e-1752512824.png</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>best phage,boost phage,vi sinh vật,thảo dược,gia cầm,gia súc</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>best + phage,kháng sinh tự nhiên,vi sinh vật,thảo dược</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>BEST + PHAGE - Bộ sản phẩm thay thế kháng sinh, cải thiện đường ruột và miễn dịch</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>2024-01-19</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WINFLO LA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Thuốc kháng sinh</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Điều trị nhiễm khuẩn</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Kháng sinh điều trị viêm phổi, nhiễm khuẩn đường hô hấp và tiêu hóa</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Đặc trị hen suyễn, viêm phổi, phổ thường hàn, E.coli, lepto, viêm phổi hóa mủ, viêm phổi dính sườn, tụ huyết trùng, hồng lỵ, sưng phù đầu, viêm ruột ỉa chảy, viêm vú, viêm tử cung, sốt bỏ ăn, bệnh kế phát tai xanh, phân xanh, phân trắng,...</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Điều trị nhiễm khuẩn đường hô hấp;Viêm phổi;Viêm ruột và bệnh kế phát</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1ml/20-35kg heo; 1ml/45-50kg trâu bò; 1ml/20kg gia cầm</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>280000</v>
-      </c>
-      <c r="J20" t="n">
-        <v>280000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Lọ tiêm</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Florfenicol</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1ml/20-50kg thể trọng</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>7 ngày</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Nơi khô, tránh ánh sáng</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>VN-2024-WINFLOLA</t>
-        </is>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-      <c r="X20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>/images/product-2a31557d-1752512845.png</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>/images/winflo-la.png;/images/gallery-winflo-la.png</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>kháng sinh,florfenicol,nhiễm khuẩn,winflo la</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>winflo la,kháng sinh,florfenicol,halife</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>WINFLO LA - Kháng sinh điều trị hiệu quả viêm phổi, nhiễm khuẩn đường ruột, kế phát tai xanh</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ANPHA NEW</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Thuốc kháng sinh</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Điều trị nhiễm khuẩn</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Kháng sinh điều trị nhiễm khuẩn hô hấp, tiêu hóa và sinh dục</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Trị nhiễm khuẩn đường hô hấp, tiêu hóa, sinh dục, nhiễm trùng da và các mô mềm trên trâu, bò, lợn, dê. Đặc trị viêm phổi, viêm màng phổi, viêm phổi hóa mủ, phổi dính sườn, ho, suyễn, lepto (bệnh nghề), phổ thường hàn, tụ huyết trùng trên gia súc, điều trị bội nhiễm trên bệnh tai xanh.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Điều trị viêm phổi;tụ huyết trùng;Nhiễm trùng sinh dục và tiêu hóa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1ml/15-20kg thể trọng, ngày tiêm 1 lần</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>190000</v>
-      </c>
-      <c r="J21" t="n">
-        <v>190000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Lọ tiêm</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Gia súc</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Enrofloxacin</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1ml/15-20kg</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>7 ngày</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Tránh ánh sáng</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>VN-2024-ANPHANEW</t>
-        </is>
-      </c>
-      <c r="W21" t="b">
-        <v>0</v>
-      </c>
-      <c r="X21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>145</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>/images/product-a0cc9ff6-1752512856.png</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>/images/anpha-new.png;/images/gallery-anpha-new.png</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>enrofloxacin,kháng sinh,viêm phổi,anpha new</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>anpha new,enrofloxacin,kháng sinh,halife</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>ANPHA NEW - Thuốc kháng sinh điều trị toàn diện nhiễm khuẩn hô hấp, tiêu hóa và sinh dục</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SORBITOL</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Giải độc &amp; bảo vệ gan</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Giải độc gan, hỗ trợ tiêu hóa, tăng cường chức năng gan</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Kích thích tiêu hóa, ăn ngon, đào thải độc tố trong gan, thận, tăng miễn dịch. Bảo vệ tế bào gan, phục hồi chức năng gan sau bệnh hoặc dùng thuốc dài ngày.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Giải độc gan;Kích thích ăn uống;Bảo vệ gan thận</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1g/1-2 lít nước hoặc 1g/1kg thức ăn, dùng liên tục 3-5 ngày</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>120000</v>
-      </c>
-      <c r="J22" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Gói</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Sorbitol, vitamin nhóm B, acid amin</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>1g/1-2 lít nước hoặc 1g/1kg thức ăn</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Khô ráo, tránh ẩm</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>VN-2024-SORBITOL</t>
-        </is>
-      </c>
-      <c r="W22" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>/images/product-8ae8c194-1752512873.png</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>/images/sorbitol.png;/images/gallery-sorbitol.png</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>sorbitol,giải độc,gan,ăn ngon,halife</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>sorbitol,giải độc gan,hỗ trợ tiêu hóa,bổ gan</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>SORBITOL - Giải độc gan, tăng miễn dịch, kích thích ăn ngon</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BOOST PHAGE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Tăng miễn dịch</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Tăng miễn dịch, giảm bệnh đường ruột</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Kết hợp chiết xuất thảo dược và chế phẩm sinh học giúp tăng miễn dịch, cân bằng hệ vi sinh vật có lợi, giảm tiêu chảy, tăng hấp thu dinh dưỡng.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Tăng miễn dịch;Giảm tiêu chảy;Cân bằng hệ tiêu hóa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Xịt miệng hoặc pha nước uống 1-2ml/con/ngày, dùng liên tục 3-5 ngày</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J23" t="n">
-        <v>150000</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Lọ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Heo, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Thảo dược, chế phẩm vi sinh</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>1-2ml/con/ngày</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Khô mát, tránh ánh nắng</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>VN-2024-BOOSTPHAGE</t>
-        </is>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>/images/product-e9d3e613-1752512905.png</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>/images/boost-phage.png;/images/gallery-boost-phage.png</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>boost phage,miễn dịch,tiêu chảy,vi sinh,thảo dược</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>boost phage,tăng miễn dịch,vi sinh,vật nuôi</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>BOOST PHAGE - Tăng miễn dịch, giảm tiêu chảy nhờ thảo dược và vi sinh vật có lợi</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>24</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CANXI VITA D3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Khoáng &amp; Canxi</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Bổ sung canxi, vitamin D3 giúp xương chắc khỏe</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tăng cường hệ xương, chống liệt chân, vẹo cổ, còi cọc, tăng hấp thu canxi và khoáng chất cần thiết cho vật nuôi phát triển.</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Bổ sung canxi;Tăng hấp thu D3;Phòng còi xương</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1g/1kg thức ăn hoặc 1g/1-2 lít nước uống</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J24" t="n">
-        <v>95000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Gói</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Canxi, Vitamin D3, Photpho</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>1g/1kg thức ăn</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Khô ráo, thoáng mát</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>VN-2024-CANXID3</t>
-        </is>
-      </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-      <c r="X24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>145</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>/images/product-e2ecd631-1752512941.png</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>/images/canxi-d3.png;/images/gallery-canxi-d3.png</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>canxi,tăng hấp thu,xương chắc khỏe,d3</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>canxi d3,bổ sung canxi,phòng còi xương,halife</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>CANXI VITA D3 - Giúp bổ sung canxi và vitamin D3 giúp phát triển hệ xương và tăng hấp thu khoáng chất</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>GLUCO KC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bù điện giải &amp; chống stress</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Bổ sung năng lượng, bù nước điện giải, chống stress cho vật nuôi</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hỗ trợ phục hồi thể lực nhanh, bù nước, cân bằng điện giải, giảm sốc nhiệt, stress do vận chuyển, tiêm vaccine, thời tiết thay đổi.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Chống stress;Bù điện giải;Bổ sung năng lượng</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1g/1-2 lít nước, dùng trong 3-5 ngày</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>89000</v>
-      </c>
-      <c r="J25" t="n">
-        <v>89000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Gói</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Glucose, KCl, NaCl, Vitamin C</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>1g/1-2 lít nước</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Khô ráo, mát</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>VN-2024-GLUCOKC</t>
-        </is>
-      </c>
-      <c r="W25" t="b">
-        <v>1</v>
-      </c>
-      <c r="X25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>/images/product-3801e6cb-1752512951.png</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>/images/gluco-kc.png;/images/gallery-gluco-kc.png</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>gluco kc,bù điện giải,chống stress,năng lượng</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>gluco kc,bù nước,giảm sốc nhiệt,vaccine</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>GLUCO KC - Giúp vật nuôi chống stress, phục hồi nhanh và cân bằng điện giải hiệu quả</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>26</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ADE TRỨNG</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Tăng đẻ &amp; chất lượng trứng</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Tăng tỉ lệ đẻ, kéo dài thời gian khai thác, trứng đẹp, đỏ lòng</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bổ sung Vitamin A, D3, E giúp tăng sản lượng trứng, cải thiện vỏ và lòng đỏ, duy trì thời gian đẻ bền vững, hạn chế cắn mổ.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Tăng đẻ;Trứng đỏ lòng;Giữ tỉ lệ đẻ cao lâu dài</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1g/1kg thức ăn hoặc 1g/1-2 lít nước liên tục 5-7 ngày/lần</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>109000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>109000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Gói</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Gia cầm</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Vitamin A, D3, E</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>1g/1kg thức ăn hoặc 1g/1-2 lít nước</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Khô ráo, tránh ẩm</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>VN-2024-ADETRUNG</t>
-        </is>
-      </c>
-      <c r="W26" t="b">
-        <v>1</v>
-      </c>
-      <c r="X26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>/images/product-8c7036ed-1752512971.png</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>/images/ade-trung.png;/images/gallery-ade-trung.png</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>ade trứng,tăng đẻ,lòng đỏ,trứng đẹp,vitamin</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>ade trứng,tăng sản lượng,trứng đỏ lòng,halife</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>ADE TRỨNG - Tăng đẻ, duy trì năng suất cao, cải thiện chất lượng trứng rõ rệt</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/public/data/halife_products.xlsx
+++ b/public/data/halife_products.xlsx
@@ -638,7 +638,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tiêu diệt virus ASF, PRRS, H5N1, H7N9 gây bệnh heo châu Phi, cúm gia cầm, lở mồm long móng,... Diệt sạch vi khuẩn E.coli, Salmonella, Clostridium và nấm mốc gây bệnh đường ruột, hô hấp. Xử lý nước uống, ngăn nguồn nhiễm khuẩn từ nước.</t>
+          <t>Thành phần: 
+- Glutaraldehyde : 150g
+- Alkyl benzyl dimethyl ammonium chloride: 100g
+- Dung môi vừa đủ: 1000ml
+Công dụng:
+- Dùng khử trùng cho chăn nuôi gia cầm, lợn, trâu, bò, cừu, ngựa. Dùng khử trùng trong trang trại chăn nuôi và dụng cụ chăn nuôi, phương tiện vận chuyển, khu vực cho ăn uống, phòng khám thú y chó, mèo và nhiều khu vực khác.
+- Là chất khử trùng phổ rộng, mang tới sự an toàn, hiệu quả , diệt sạch các loại virus, vi khuẩn, nấm gây bệnh trên giá súc, gia cầm như: Dịch tả lợn châu phi, tai xanh (PRRS), lở mômg long móng, tiêu chảy (T.G.E), Parvo, Lepto, sảy thai truyền nhiễm, tụ huyết trùng, các bệnh cúm gia cầm, Gumboro, Newcastle, CRD, dịch tả vịt… 
+Liều lượng và cách dùng:
+Pha theo tỉ lệ chỉ định, phun xịt đều lên bề mặt cần sát trùng:
+- Tiêu độc sát trùng chuồng trại:
++ Khi không có dịch bệnh: pha loãng 15-20 ml trong 10 lít nước sạch, phun đèu lên chuồng và nền chuống, 5-7 ngày phun lại 1 lần.
++ Khi có dịch bệnh: Pha loãng 50-100 ml cho 10 lít nước sạch, phun  1-2 lần, liên tục 3-5 ngày hoặc cho đến khi hết dịch. 
+- Tiêu độc phương tiện vận chuyển, sát trùng lò ấp, máy ấp trứng: 20 ml thuốc pha trong 10 lít nước sạch, phun đều lên xe vận chuyển, lò ấp. 
+- Khử trùng trứng: 10 ml pha trong 10 lít nước sạch. 
+- Khử trùng nước : 5 ml pha trong 10 lít nước sạch. 
+- Tiêu độc xác súc vật chết, phân súc vật, hố sát trùng:  70 ml thuốc pha trong 10 lít nước sạch, phun ướt đều xác súc vật chét, phân súc vật.
+Chống chỉ định:
+- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc
+Bảo quản:
+- Trong bao bì kín, nơi khô ráo thoáng mát, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -767,7 +786,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -802,7 +821,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cung cấp Canxi hữu cơ và Vitamin D3 giúp hấp thụ tốt hơn. Tăng sản lượng trứng, kéo dài thời gian khai thác, vỏ bóng, đều và chắc. Hỗ trợ phục hồi xương, tăng miễn dịch và sức đề kháng cho vật nuôi.</t>
+          <t xml:space="preserve">Cung cấp Canxi hữu cơ và Vitamin D3 giúp hấp thụ tốt hơn. Tăng sản lượng trứng, kéo dài thời gian khai thác, vỏ bóng, đều và chắc. Hỗ trợ phục hồi xương, tăng miễn dịch và sức đề kháng cho vật nuôi.
+Thành phần:
+Vitamin B1*min: 2000mg
+Vitamin D3*min: 1000000IU
+Vitamin B6*min: 2000mg
+Sorbitol*min: 5000mg
+Canxi*min - max: 7,000.00 - 8,000.00mg
+Biotin*min: 2000mg
+Vitamin C*min: 1000mg
+Đồng*min - max: 500.00 - 570.00mg
+Sắt*min - max: 600.00 - 800.00mg
+Tá dược vừa đủ: 1000g 
+Sản phẩm không chứa kháng sinh, hoocmon v à các chất độc hại. 
+Công dụng:
+*Cung cấp Canxi hữu cơ và Vitamin D3 tăng khả năng hấp thu Canxi nhanh hơn. 
+- Tăng sản lượng trứng, kéo dài thời gian khai thác trứng trong thời gian đẻ đỉnh cao. Vỏ trứng dày, bóng hơn, không vỡ.
+- Hỗ trợ giảm tỉ lệ bại liệt, lông xơ, cắn mổ lông
+Tăng miễn dịch, tăng phục hồi và nâng cao sức đề kháng cho vật nuôi.
+Hỗ trợ chống còi xương, mềm xương ở vật nuôi.
+Liều lượng và cách dùng:
+Hòa vào nước uống hoặc trộn thức ăn, dùng liên tục trong 3-5 ngày. 
+- Gà, vịt, cút đẻ: 5ml/ 10 lít nước/ 40-50 con.
+- Gà, vịt, cút thịt: 5ml/20 ml nước/100 con.
+- Lợn nái: 20 ml/ nái/ ngày. 
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi. 
+Lưu ý: nên sử dụng kết hợp sản phẩm men sống và sản phẩm siêu úm gà vịt để đạt hiệu quả cao nhất. 
+Bảo quản:
+Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C. </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -867,7 +913,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C. </t>
+          <t>Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -932,7 +978,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -967,7 +1013,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cung cấp vitamin K3, C cho cơ thể gia súc, gia cầm, giúp giữ vững thành mạch, giúp cầm máu, tăng sức đề kháng cơ thể vật nuôi, giải nhiệt, tăng lực cho vật nuôi. </t>
+          <t>Thành phần:
+Vitamine K3 min: 5000 mg
+Vitamin C min: 30.000 mg
+Tá dược vừa đủ: 1000 g
+Công dụng: 
+Cung cấp vitamin K3, C cho cơ thể gia súc, gia cầm, giúp giữ vững thành mạch, giúp cầm máu, tăng sức đề kháng cơ thể vật nuôi, giải nhiệt, tăng lực cho vật nuôi. 
+Liều lượng và cách dùng:
+Cách dùng: Pha nước uống hoặc  trộn vào thức ăn.
+Liều dùng:
+- Gà, vịt, ngan, ngỗng: pha 3 g/ lít nước uống hoặc trộn 3 g/ kg thức ăn. 
+- Lợn, trâu, bò: Pha 100 g/ 50 lít nước uống hoặc trộn 100 g/ 50-60 kg thức ăn.
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1009,10 +1067,10 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cách dùng: Pha nước uống hoặc  trộn vào thức ăn.
+          <t>Cách dùng: Pha nước uống hoặc  trộn vào thức ăn.
 Liều dùng:
 Gà, vịt, ngan, ngỗng: pha 3 g/ lít nước uống hoặc trộn 3 g/ kg thức ăn. 
-Lợn, trâu, bò: Pha 100 g/ 50 lít nước uống hoặc trộn 100 g/ 50-60 kg thức ăn. </t>
+Lợn, trâu, bò: Pha 100 g/ 50 lít nước uống hoặc trộn 100 g/ 50-60 kg thức ăn.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1091,7 +1149,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1126,8 +1184,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trị bệnh phế quản phổi cấp và mãn tính liên quan đến tiết chất nhầy trên bê, lợn, gia cầm, chó, mèo.
-Giảm ho, tiêu đờm, chống co thắt phế quản trong các bệnh viêm phế quản, viêm thanh quản truyền nhiễm, viêm phổi, suyễn, sổ mũi truyền nhiễm, CRD, CCRD. </t>
+          <t>Thành phần:
+Bromhexin HCl: 1g
+Tá dược vừa đủ: 100 g
+Công dụng:
+- Trị bệnh phế quản phổi cấp và mãn tính liên quan đến tiết chất nhầy trên bê, lợn, gia cầm, chó, mèo.
+- Giảm ho, tiêu đờm, chống co thắt phế quản trong các bệnh viêm phế quản, viêm thanh quản truyền nhiễm, viêm phổi, suyễn, sổ mũi truyền nhiễm, CRD, CCRD.
+Liều lượng và cách dùng:
+Pha nước uống hoặc trộn với thức ăn dùng liên tục 3 – 5 ngày theo liều:
+– Gà, vịt, ngan, cút: 1g/10 – 12 kg TT hoặc 1 g/1 -2 lít nước uống hoặc trộn 1 g/2 kg thức ăn.
+– Lợn và gia súc khác: 1 g/18 – 20 kg thể trọng.
+Chống chỉ định:
+- Động vật mẫn cảm với thành phần của thuốc. 
+- Không sử dụng cho động vật 4 tuần trước và trong khi sinh sản. 
+- Không dùng cho động vật lấy trứng và sữa. 
+Thời gian ngưng sử dụng thuốc:
+Thịt và nội tạng: 7 ngày
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1245,7 +1319,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1280,7 +1354,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trị nhiễm trùng đường tiêu hóa, hô hấp, niệu sinh dục, nhiễm khuẩn huyết, nhiễm trùng da, vết thương trên trâu, bò, bê, nghé, dê, cừu, lợn.</t>
+          <t>Thành phần:
+Trong 100ml có chứa:
+- Enrofloxacin: 10 g
+- Dung môi vừa đủ: 100 ml
+Công dụng:
+Trị nhiễm trùng đường tiêu hóa, hô hấp, niệu sinh dục, nhiễm khuẩn huyết, nhiễm trùng da, vết thương trên trâu, bò, bê, nghé, dê, cừu, lợn.
+Chỉ định của BSTY:
+Đặc trị viêm ruột, tiêu chảy do E.coli, Salmonella, viêm phổi, viêm vú, viêm tử cung, viêm khớp, hen khẹc trên gia súc, gia cầm.
+Liều lượng và cách dùng:
+Tiêm mũi duy nhất, tiêm bắp hoặc tiêm dưới da
+- Gà, vịt, ngan, cút: 1ml/6-8kg TT.
+- Lợn: 1ml/8-12kg TT.
+- Lợn con: 1ml/6-7kg TT.
+- Trâu, bò, dê, cừu: 1ml/15-20kg TT.
+Trường hợp bệnh nặng: Tiêm nhắc lại sau 36-48h.
+Chống chỉ định:
+Không sử dụng cho vật nuôi mẫn cảm với các thành phần của thuốc.
+Thời gian ngưng sử dụng thuốc:
+- Trâu, bò, bê, nghé, dê, cừu: 21 ngày.
+- Lợn: 14 ngày.
+- Gia cầm: 7 ngày.
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1402,7 +1498,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1437,12 +1533,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kích thích mọc lông, chống cắn mổ
-Bổ sung vitamin thiết yếu và khoáng chất vi lượng cho gia cầm
-Vỗ béo, chống còi, tăng sản lượng thịt, tăng số lượng và chất lượng trứng. 
-Tạo màu vàng đẹp cho lòng đỏ trứng
-Nâng cao năng suất cho gia cầm sinh sản 
-Trứng to, vỏ dày, tỷ lệ đẻ cao, kéo dài.</t>
+          <t xml:space="preserve">Thành phần:
+- Vitamin B1 (min): 10000mg 
+- Vitamin B2(min): 3000 mg
+- Vitamin B6(min): 300 mg
+- Biotin (min): 450 mg
+- Kẽm (min- max): 70-150 mg
+- Lysine (min): 2000 mg
+- Vitamin D3 (min): 2000 mg
+- Canxi (min-max): 2000-3500mg 
+- Tá dược vừa đủ: 1000 g 
+Thành phần bổ sung hỗn hợp 10 lại enzyme hữu hiệu: Phytase, amylase, xylanase, protease, mannanase, cellulose, pectinase, B- Glucannsase, a- Galactosidase, lipase. 
+Sản phẩm không chứa chất kháng sinh, hoocmon và các chất độc hại. 
+Công dụng:
+- Kích thích mọc lông, chống cắn mổ
+- Bổ sung vitamin thiết yếu và khoáng chất vi lượng cho gia cầm
+- Vỗ béo, chống còi, tăng sản lượng thịt, tăng số lượng và chất lượng trứng. 
+- Tạo màu vàng đẹp cho lòng đỏ trứng
+- Nâng cao năng suất cho gia cầm sinh sản 
+- Trứng to, vỏ dày, tỷ lệ đẻ cao, kéo dài.
+Liều lượng và cách dùng:
+- Pha nước uống hoặc trộn thức ăn.
+- Gà, vịt, lợn con: 100 g/ 50-100 kg thức ăn 
+- Lợn nái, lợn con: 20g/20-30 kg thức ăn. 
+- Trâu, bò, dê, cừu, bê, nghé: 20 g/ 50 kg thức ăn. 
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ c. </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1570,7 +1686,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1605,12 +1721,38 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bổ sung probiotic,acid amin, hỗn hợp vitamin và khoáng thiết yếu cho vật nuôi, công thức đặc biệt bổ sung dưỡng chất cho đối tượng con nái để: 
+          <t>Thành phần:
+Trong 1000g có chứa:
+- Zn (Min - max): 1600 -1800 mg/kg
+- Fe (Min - max): 3000 - 5000 mg/kg
+- Lysine (min): 15000 mg/kg
+- Vitamin A (min): 2.500.000 IU/kg
+- Vitamin D (min): 1.000.000 IU/kg
+- Vitamin E (min): 620 mg/kg
+- Biotin (min): 400 mg/kg
+- Senlen (min - max): 38-54 mg/kg
+- Tá dược vừa đủ: 1000g
+Thành phần nguyên liệu: 
+- Bổ sung vi sinh vật có lợi: lactobacillus; sacharomyces; bacillus subtilis
+- Bổ sung hỗn hợp 10 loại enzyme : Bổ sung hỗn hợp 10 enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)
+- Bổ sung thành phần thảo dược: Mộc hương, hoài sơn, ý dĩ, thần khúc, sơn tra.
+Công dụng:
+Bổ sung probiotic,acid amin, hỗn hợp vitamin và khoáng thiết yếu cho vật nuôi, công thức đặc biệt bổ sung dưỡng chất cho đối tượng con nái để: 
 * Tăng cường sức khỏe, Tăng tỷ lệ đậu thai và tỷ lệ đẻ, Tăng số con trong lứa.
 * Đối với nái chửa: Cân bằng dinh dưỡng, bào thai phát triển tốt hơn, đẻ dễ dàng hơn.
 * Đối với nái chờ phối: Sử dụng sản phẩm thường xuyên giúp rút ngắn thời gian lên giống sau cai sữa, động dục mạnh hơn.
 * Phòng nứt móng, sừng hóa da.
-* Khung xương phát triển mạnh, hạn chế bại liệt.</t>
+* Khung xương phát triển mạnh, hạn chế bại liệt.
+Liều lượng và cách dùng:
+CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.
+LIỀU DÙNG: 
+- Nái chửa : 1kg trộn với 400 – 600 kg thức ăn hỗn hợp.
+- Nái hậu bị và nái chờ phối : 1kg trộn với 1.000 kg thức ăn hỗn hợp.
+- Hòa nước: 1g/2-3 lít nước uống.
+Lưu ý : Có thể dùng chung với kháng sinh để phòng bệnh.
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1744,7 +1886,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1779,7 +1921,43 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bổ sung vitamin, acid amin, enzyme và protein giúp vật nuôi tăng trưởng nhanh, hạn chế dùng kháng sinh, phục hồi sau mất sữa, tăng đề kháng, tiêu hóa tốt, xuất chuồng sớm</t>
+          <t xml:space="preserve">Thành phần:
+Trong 1000g có chứa:
+- Protein thô* min: 5%
+- Vitamin A(min): 800.000 IU/kg
+- Vitamin D (min): 160.000 IU/kg
+- Vitamin E (min): 1800 mg/kg
+- Vitamin B1 (min): 1200 mg/kg
+- Vitamin B2 (min) 800 mg/kg
+- Vitamin B6 (min): 1000 mg/kg
+- Amylase (min): 2400 IU/kg
+- Protease (min): 4000 IU/kg
+- Lysine (min): 8000 mg/kg
+- Methionine (min): 6000 mg/kg
+- Sorbitol (min): 5000 mg/kg
+- Tá dược vừa đủ: 1000g 
+Thành phần nguyên liệu: 
+Bổ sung hỗn hợp 10 loại enzyme : Bổ sung hỗn hợp 10 enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)
+Công dụng:
+* Công thức dinh dưỡng hoàn chỉnh, hàm lượng đạm cao, hiệu quả vỗ béo nhanh, xuất chuồng sớm, hạn chế dùng kháng sinh trong chăn nuôi gia súc gia cầm.
+* Giải pháp nâng cao hiệu quả chăn nuôi. Bổ sung vitamin, acid amin và enzyme cho vật nuôi trong các trường hợp cần thiết.
+* Bổ sung protein 1 cách cân đối. Có thể bổ sung thay thế cho sữa mẹ khi nái mất sữa trong những ngày ốm kém do vận chuyển xa.
+* Kích thích tính thèm ăn và tăng cường tiêu hóa, hấp thu, cải thiện hiệu quả thức ăn.
+* Giảm tỷ lệ chết, tăng cường sức đề kháng, tăng cường khả năng miễn dịch cho vật nuôi.
+* Giảm tiêu tốn thức ăn, rút ngắn thời gian nuôi.
+* Vật nuôi lớn nhanh, khỏe mạnh, lợn ích chăn nuôi vượt trội.
+* Vật nuôi lớn nhanh, khoẻ mạnh, lợi ích tăng trưởng chăn nuôi vượt trội.
+Liều lượng và cách dùng:
+CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.
+LIỀU DÙNG: 
+* Hòa nước uống: 1g/ 2-3 lít nước.
+* Trộn thức ăn: cho ăn giai đoạn trước khi xuất. 
+Gia cầm: 1kg/ 500 - 1000 kg thức ăn.
+Gia súc: 1kg/ 300 - 500 kg thức ăn.
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.
+</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1906,7 +2084,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1941,7 +2119,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trị viêm tử cung trước và sau sinh, viêm vú, mất sữa ở gia súc. Trị viêm phổi, CRD, CCRD, bệnh tiêu hóa.</t>
+          <t>Thành phần:
+- Oxytetracycline: 30g
+- Flunixin: 2g 
+- Dung môi vừa đủ: 100ml
+Công dụng:
+- Đặc trị các bệnh đường tiết niệu, sinh dục như: viêm tử cung trước và sau khi sinh, viêm vú, mất sữa (MMA), ở gia súc, heo. 
+- Điều trị các bệnh nhiễm trùng đường hô hấp: viêm phổi, CRD, CCRD; các bệnh đường tiêu hoá: viêm ruột, viêm ruột tiêu chảy...
+Liều lượng và cách dùng:
+- Tiêm bắp sâu 1 liều duy nhất. 
+- Liều lượng: 1 ml / 10 kg thể trọng/ngày. 
+- Thể tích tối đa trên mỗi vị trí tiêm: 15 ml.
+Chống chỉ định:
+- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc. 
+- Không sử dụng cho động vật bị suy gan, thận.
+Thời gian ngưng sử dụng thuốc:
+Lấy thịt:
+Trâu, bò, dê, cừu, heo: 35 ngày.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2068,7 +2262,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2103,7 +2297,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Giúp gia súc non phát triển, tăng sinh sản, giảm suy nhược, thiếu máu, tăng chuyển hóa.</t>
+          <t>Thành phần:
+- Butaphosphan: 10 g
+- Vitamin B12: 5mg
+- Dung môi vừa đủ: 100 ml
+Công dụng:
+- Điều trị các rối loạn chuyển hoá cấp và mãn tính. Rối loạn phát triển dinh dưỡng ở gia súc non, kích thích trao đổi chất, tăng trọng lớn nhanh, ngừa stress. Hỗ trợ điều trị bệnh ghép, E.coli, CRD, heo tai xanh.
+- Tăng cường khả năng sinh sản, tăng tỉ lệ trứng ở gà, vịt, cút, kích sữa ở gia súc, hỗ trợ trị bệnh hậu sản, phòng sốt sữa, bại liệt sau khi sinh, hỗ trợ điều trị vô sinh.
+- Điều trị các trường hợp kiệt sức, giảm sức đề kháng, suy nhược, thiếu máu, hồi phục sức khoẻ nhanh, phòng chống còi xương duy dinh dưỡng. Tăng chuyển hoá, giúp heo con đồng đều, cứng cáp, chống còi cọc.
+Liều lượng và cách dùng:
+Duùng tiêm dưới da, tiêm bắp hoặc tiêm tĩnh mạch. 
+- Trâu, bò, ngựa: 10-25 ml/con (Chỉ dùng tiêm tĩnh mạch).
+- Ngựa non, bê, nghé: 5-12 ml/con (Chỉ dùng tiêm tĩnh mạch).
+- Lợn, cừu, dê: 2,5-10 ml/con.
+- Lợn con: 1-2.5 ml/con (Chỉ tiêm dưới da).
+- Gia cầm: 0.5-1 ml/con. 
+ Lặp lại điều trị trong 1-2 tuần (nếu cần).
+Chống chỉ định:
+Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.
+Bảo quản:
+Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2230,7 +2443,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2265,15 +2478,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công thức, tá dược, dung môi dung hòa đặc biệt, giúp bộ đôi sản phẩm tiêu diệt hầy hết các loại vi khuẩn gây ra bệnh đường hô hấp cho gia súc:
-* Heo:
-- Phòng và trị bệnh viêm đường hô hấp phức hợp (heo hắt hơi từng hồi, chảy nước mũi, ho, khó thở, thở nhanh và nhiều, heo há hốc mồm để thở)
-- Phòng và trị bệnh viêm phổi, suyễn, tụ huyết trùng, viêm phổi - màng hổi, bệnh Glaser, viêm teo xoang mũi
-- Phòng các bệnh bội nhiễm và kế phát khi heo bệnh tai xanh (PRRS) và lở mồm long móng (FMD)
-* Trâu bò, dê, cừu:
-- Trị các bệnh đường hô hấp như viêm phổi, tụ huyết trùng, viêm hô hấp phức hợp, 
-- Viêm kết giác mạc,
-- Phòng các bệnh bội nhiễm và kế phát khi trâu bò, dê, cừu bệnh lở mồm long móng. bệnh thối móng"</t>
+          <t>THÀNH PHẦN:
+Trong 100ml có chứa:
+- Florfenicol: 45g
+- Dung môi vừa đủ: 100ml
+Công dụng:
+Công thức, tá dược, dung môi dung hòa đặc biệt, giúp bộ đôi sản phẩm tiêu diệt hầy hết các loại vi khuẩn gây ra bệnh đường hô hấp cho gia súc
+Heo:
+* Phòng và trị bệnh viêm đường hô hấp phức hợp (heo hắt hơi từng hồi, chảy nước mũi, ho, khó thở, thở nhanh và nhiều, heo há hốc mồm để thở)
+* Phòng và trị bệnh viêm phổi, suyễn, tụ huyết trùng, viêm phổi - màng hổi, bệnh Glaser, viêm teo xoang mũi
+* Phòng các bệnh bội nhiễm và kế phát khi heo bệnh tai xanh (PRRS) và lở mồm long móng (FMD)
+Trâu bò, dê, cừu:
+* Trị các bệnh đường hô hấp như viêm phổi, tụ huyết trùng, viêm hô hấp phức hợp, 
+* Viêm kết giác mạc,
+* Phòng các bệnh bội nhiễm và kế phát khi trâu bò, dê, cừu bệnh lở mồm long móng. bệnh thối móng
+Cách dùng và liều dùng:
+CÁCH DÙNG: Tiêm bắp hoặc tiêm dưới da một liều duy nhất
+LIỀU DÙNG: Lấy 1ml ANPHA NEW + 1ml WINFLO LA lắc đều. Sau đó lấy 2 ml hỗn hợp dung dịch kháng sinh tiêm cho:
+HEO: 2ml/15-20 kg thể trọng đối với bệnh nặng và 2ml/25-30 kg thể trọng đối với bệnh nhẹ. Tiêm bắp 1 liều duy nhất
+TRÂU BÒ: 2ml/40kg thể trọng
+DÊ, CỪU: 2ml /40 kg thể trọng
+Chỉ định của BSTY:
+Đặc trị hen suyễn, viêm phổi, phó thương hàn, E.coli, lepto, viêm phổi hóa mủ, viêm phổi dính sườn, tụ huyết trùng, hồng lỵ, E.coli, sưng phù đầu, viêm ruột ỉa chảy, viêm vú, viêm tử cung, nhiễm trùng huyết sau sinh, sốt bỏ ăn, bệnh kế phát tai xanh, sốt đỏ (PRRS) do nhiều loại vi khuẩn bội nhiễm, tiêu chảy phân xanh, phân trắng ở gà, vịt.
+Chống chỉ định:
+- Không sử dụng cho vật nuôi mẫn cảm với các thành phần của thuốc.
+- Không sử dụng cho động vật lấy sữa thương phẩm và trong thời gian cho con bú
+Thời gian ngừng sử dụng thuốc:
+46 ngày trước khi giết mổ.
+Bảo quản:
+Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2403,7 +2636,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2434,7 +2667,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ĐẶC TRỊ VIÊM VÚ, VIÊM TỬ CUNG, VIÊM MÓNG, VIÊM KHỚP, VIÊM PHỔI, PHỔI DÍNH SƯỜN, SỐT, BỎ ĂN KHÔNG RÕ NGUYÊN NHÂN</t>
+          <t>Thành phần:
+- Ceftiofur (dạng hydroclorid): 5 g
+- Ketoprofen: 5 g
+- Dung môi vừa đủ: 100 ml
+Công dụng:
+- Trị hội chứng MMA (viêm tử cung, viêm vú, mất sữa)
+- Trị viêm phổi, viêm phế quản, viêm phổi dính sườn, hen suyễn, tụ huyết trùng
+- Trị tiêu chảy do E.coli, Salmonella, sưng phù đầu, viêm ruột tiêu chảy, phân trắng lợn con, viêm da, Lepto, nhiễm trùng huyết, sốt bỏ ăn không rõ nguyên nhân. Bệnh kế phát do LMLM, TNRS, VDNC.
+- Trị viêm khớp, thối móng, viêm vú, viêm tử cung ở trâu bò
+Liều lượng và cách dùng:
+- Tiêm bắp 1 liều duy nhất. Lắc kĩ trước khi sử dụng.
+- Lấy 1ml/ 50 kg thể trọng mỗi lần tiêm. Dùng từ 3-5 ngày liên tục.
+- Không tiêm quá 16 ml tại bất kì vị trí tiêm bắp nào. Các lần tiếp theo phải được tiêm ở vị trí khác.
+Chống chỉ định:
+- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.
+- Không sử dụng cho động vật suy gan, suy thận.
+Thời gian ngưng sử dụng thuốc:
+Lấy thịt và nội tạng: 08 ngày
+Bảo quản:
+Trong bao bì kín, nơi khô ráo thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -2537,7 +2789,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2809,10 +3061,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Xử lí hoàn toàn các vi khuẩn gây bệnh như Salmonella spp, Escherichia coli và C.perfringens trên gia súc, gia cầm.
-Cải thiện sức khoẻ đường ruột, sản sinh vi khuẩn có lợi, hấp thu thức ăn triệt để, cải thiện FCR
-Sử dụng tất cả các giai đoạn của vật nuôi. 
-Kết hợp với sản phẩm Boost phage giúp tăng năng suất, hiệu quả chăn nuôi, sớm xuất bán</t>
+          <t xml:space="preserve">Thành phần:
+Bacillus spp(min): 1x107
+Dung môi vừa đủ: 1000ml 
+Công dụng:
+- Xử lí hoàn toàn các vi khuẩn gây bệnh như Salmonella spp, Escherichia coli và C.perfringens trên gia súc, gia cầm.
+- Cải thiện sức khoẻ đường ruột, sản sinh vi khuẩn có lợi, hấp thu thức ăn triệt để, cải thiện FCR
+- Sử dụng tất cả các giai đoạn của vật nuôi. 
+- Kết hợp với sản phẩm Boost phage giúp tăng năng suất, hiệu quả chăn nuôi, sớm xuất bán
+Liều lượng và cách dùng:
+Lắc đều trước khi sử dụng. 
+- Phòng bệnh: 1ml pha với 2 lít nước, dùng cho 30 kg thể trọng vật nuôi.
+- Vật nuôi giai đoạn úm: Thay thế kháng sinh, dùng liên tục từ 5- 7 ngày khi bắt đầu giai đoạn úm. Sau đó, sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục từ 2-3 ngày.  
+- Gia súc, gia cầm: Sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục 2-3 ngày. 
+Bảo quản:
+Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C. </t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2911,7 +3174,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">

--- a/public/data/halife_products.xlsx
+++ b/public/data/halife_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,26 +638,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thành phần: 
-- Glutaraldehyde : 150g
-- Alkyl benzyl dimethyl ammonium chloride: 100g
-- Dung môi vừa đủ: 1000ml
-Công dụng:
-- Dùng khử trùng cho chăn nuôi gia cầm, lợn, trâu, bò, cừu, ngựa. Dùng khử trùng trong trang trại chăn nuôi và dụng cụ chăn nuôi, phương tiện vận chuyển, khu vực cho ăn uống, phòng khám thú y chó, mèo và nhiều khu vực khác.
-- Là chất khử trùng phổ rộng, mang tới sự an toàn, hiệu quả , diệt sạch các loại virus, vi khuẩn, nấm gây bệnh trên giá súc, gia cầm như: Dịch tả lợn châu phi, tai xanh (PRRS), lở mômg long móng, tiêu chảy (T.G.E), Parvo, Lepto, sảy thai truyền nhiễm, tụ huyết trùng, các bệnh cúm gia cầm, Gumboro, Newcastle, CRD, dịch tả vịt… 
-Liều lượng và cách dùng:
-Pha theo tỉ lệ chỉ định, phun xịt đều lên bề mặt cần sát trùng:
-- Tiêu độc sát trùng chuồng trại:
-+ Khi không có dịch bệnh: pha loãng 15-20 ml trong 10 lít nước sạch, phun đèu lên chuồng và nền chuống, 5-7 ngày phun lại 1 lần.
-+ Khi có dịch bệnh: Pha loãng 50-100 ml cho 10 lít nước sạch, phun  1-2 lần, liên tục 3-5 ngày hoặc cho đến khi hết dịch. 
-- Tiêu độc phương tiện vận chuyển, sát trùng lò ấp, máy ấp trứng: 20 ml thuốc pha trong 10 lít nước sạch, phun đều lên xe vận chuyển, lò ấp. 
-- Khử trùng trứng: 10 ml pha trong 10 lít nước sạch. 
-- Khử trùng nước : 5 ml pha trong 10 lít nước sạch. 
-- Tiêu độc xác súc vật chết, phân súc vật, hố sát trùng:  70 ml thuốc pha trong 10 lít nước sạch, phun ướt đều xác súc vật chét, phân súc vật.
-Chống chỉ định:
-- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc
-Bảo quản:
-- Trong bao bì kín, nơi khô ráo thoáng mát, nhiệt độ dưới 30 độ C.</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&amp;nbsp;&lt;div&gt;- Silver (nitrate) : 1000ppm&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ: 1000ml&amp;nbsp;&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Dùng khử trùng chuồng trại, dụng cụ, phương tiện vận chuyển, phòng khám thú y, giải pháp thay thế hóa chất, ưu điểm vượt trội của Nano Bạc an toàn cho con người và vật nuôi.&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Là chất khử trùng phổ rộng, diệt sạch các loại virus, vi khuẩn, nấm gây bệnh trên gia súc, gia cầm như: Dịch tả heo châu phi, tai xanh (PRRS), lở mồm long móng, tiêu chảy (T.G.E), Parvo, Lepto, sảy thai truyền nhiễm, tụ huyết trùng, các bệnh cúm gia cầm, Gumboro, Newcastle, CRD, dịch tả vịt…&lt;/div&gt;&lt;div&gt;- Khử trùng nguồn nước, không mùi, không gây oxy hóa hay ăn mòn thiết bị.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Sát trùng vết thương hở, vết loét, viêm da do vi khuẩn.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Sát trùng vú bò sữa, dê sữa trước khi thu hoạch sữa, hạn chế tối đa tình trạng viêm vú.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Sát trùng, thụt rửa tử cung, hỗ trợ điều trị hiệu quả bệnh viêm vú, viêm tử cung, tổn thương niêm mạc tử cung...&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG&lt;/b&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Dùng sát trùng chuồng trại khi có áp lực dịch tả heo châu phi, lở mồm long móng, tai xanh, tiêu chảy do virus trên heo, cúm gia cầm, các bệnh do virus trên gia cầm với liều dùng: 1 lít NANO BẠC AG+&amp;nbsp; pha với 200 – 300 lít nước sạch.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Phun sát trùng định kỳ với liều dùng: 1 lít NANO BẠC AG+ pha với 400 - 500 lít nước sạch.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Xử lý vết thương hở, viêm da, lở loét do ve ghẻ, viêm loét do lở mồm long móng với liều dùng: 10 ml NANO BẠC AG+&amp;nbsp; pha với 10 ml nước sạch.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Lau rửa bầu vú heo mẹ với liều dùng: 10 ml NANO BẠC AG+ pha với 1 lít nước sạch.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Thụt rửa tử cung khi heo mẹ bị viêm nhiễm với liều dùng: 10 ml NANO BẠC AG+ pha với 1 lít nước sạch.&lt;/div&gt;&lt;div&gt;-&amp;nbsp;Xử lý nguồn nước uống với liều dùng: 10 ml&amp;nbsp;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;0 ngày.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc&amp;nbsp;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Trong bao bì kín, nơi khô ráo thoáng mát, nhiệt độ dưới 30 độ C.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -786,7 +767,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -821,34 +802,9 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cung cấp Canxi hữu cơ và Vitamin D3 giúp hấp thụ tốt hơn. Tăng sản lượng trứng, kéo dài thời gian khai thác, vỏ bóng, đều và chắc. Hỗ trợ phục hồi xương, tăng miễn dịch và sức đề kháng cho vật nuôi.
-Thành phần:
-Vitamin B1*min: 2000mg
-Vitamin D3*min: 1000000IU
-Vitamin B6*min: 2000mg
-Sorbitol*min: 5000mg
-Canxi*min - max: 7,000.00 - 8,000.00mg
-Biotin*min: 2000mg
-Vitamin C*min: 1000mg
-Đồng*min - max: 500.00 - 570.00mg
-Sắt*min - max: 600.00 - 800.00mg
-Tá dược vừa đủ: 1000g 
-Sản phẩm không chứa kháng sinh, hoocmon v à các chất độc hại. 
-Công dụng:
-*Cung cấp Canxi hữu cơ và Vitamin D3 tăng khả năng hấp thu Canxi nhanh hơn. 
-- Tăng sản lượng trứng, kéo dài thời gian khai thác trứng trong thời gian đẻ đỉnh cao. Vỏ trứng dày, bóng hơn, không vỡ.
-- Hỗ trợ giảm tỉ lệ bại liệt, lông xơ, cắn mổ lông
+          <t>&lt;b&gt;THÀNH PHẦN:&amp;nbsp;&lt;/b&gt;&lt;div&gt;- Vitamin B1*min: 2000mg&lt;/div&gt;&lt;div&gt;- Vitamin D3*min: 1000000IU&lt;/div&gt;&lt;div&gt;- Vitamin B6*min: 2000mg&lt;/div&gt;&lt;div&gt;- Sorbitol*min: 5000mg&lt;/div&gt;&lt;div&gt;- Canxi*min - max: 7,000.00 - 8,000.00mg&lt;/div&gt;&lt;div&gt;- Biotin*min: 2000mg&lt;/div&gt;&lt;div&gt;- Vitamin C*min: 1000mg&lt;/div&gt;&lt;div&gt;- Đồng*min - max: 500.00 - 570.00mg&lt;/div&gt;&lt;div&gt;- Sắt*min - max: 600.00 - 800.00mg&lt;/div&gt;&lt;div&gt;- Tá dược vừa đủ: 1000g&lt;/div&gt;&lt;div&gt;Sản phẩm không chứa kháng sinh, hoocmon v à các chất độc hại.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Cung cấp Canxi hữu cơ và Vitamin D3 tăng khả năng hấp thu Canxi nhanh hơn.&lt;/div&gt;&lt;div&gt;- Tăng sản lượng trứng, kéo dài thời gian khai thác trứng trong thời gian đẻ đỉnh cao. Vỏ trứng dày, bóng hơn, không vỡ.&lt;/div&gt;&lt;div&gt;- Hỗ trợ giảm tỉ lệ bại liệt, lông xơ, cắn mổ lông
 Tăng miễn dịch, tăng phục hồi và nâng cao sức đề kháng cho vật nuôi.
-Hỗ trợ chống còi xương, mềm xương ở vật nuôi.
-Liều lượng và cách dùng:
-Hòa vào nước uống hoặc trộn thức ăn, dùng liên tục trong 3-5 ngày. 
-- Gà, vịt, cút đẻ: 5ml/ 10 lít nước/ 40-50 con.
-- Gà, vịt, cút thịt: 5ml/20 ml nước/100 con.
-- Lợn nái: 20 ml/ nái/ ngày. 
-Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi. 
-Lưu ý: nên sử dụng kết hợp sản phẩm men sống và sản phẩm siêu úm gà vịt để đạt hiệu quả cao nhất. 
-Bảo quản:
-Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C. </t>
+Hỗ trợ chống còi xương, mềm xương ở vật nuôi.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Hòa vào nước uống hoặc trộn thức ăn, dùng liên tục trong 3-5 ngày.&lt;/div&gt;&lt;div&gt;- Gà, vịt, cút đẻ: 5ml/ 10 lít nước/ 40-50 con.&lt;/div&gt;&lt;div&gt;- Gà, vịt, cút thịt: 5ml/20 ml nước/100 con.&lt;/div&gt;&lt;div&gt;- Lợn nái: 20 ml/ nái/ ngày.&lt;/div&gt;&lt;div&gt;Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.&lt;/div&gt;&lt;div&gt;Lưu ý: nên sử dụng kết hợp sản phẩm men sống và sản phẩm siêu úm gà vịt để đạt hiệu quả cao nhất.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -978,7 +934,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1013,19 +969,8 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thành phần:
-Vitamine K3 min: 5000 mg
-Vitamin C min: 30.000 mg
-Tá dược vừa đủ: 1000 g
-Công dụng: 
-Cung cấp vitamin K3, C cho cơ thể gia súc, gia cầm, giúp giữ vững thành mạch, giúp cầm máu, tăng sức đề kháng cơ thể vật nuôi, giải nhiệt, tăng lực cho vật nuôi. 
-Liều lượng và cách dùng:
-Cách dùng: Pha nước uống hoặc  trộn vào thức ăn.
-Liều dùng:
-- Gà, vịt, ngan, ngỗng: pha 3 g/ lít nước uống hoặc trộn 3 g/ kg thức ăn. 
-- Lợn, trâu, bò: Pha 100 g/ 50 lít nước uống hoặc trộn 100 g/ 50-60 kg thức ăn.
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Vitamine K3 min: 5000 mg&lt;/div&gt;&lt;div&gt;Vitamin C min: 30.000 mg&amp;nbsp;&lt;/div&gt;&lt;div&gt;á dược vừa đủ: 1000 g&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Cung cấp vitamin K3, C cho cơ thể gia súc, gia cầm, giúp giữ vững thành mạch, giúp cầm máu, tăng sức đề kháng cơ thể vật nuôi, giải nhiệt, tăng lực cho vật nuôi.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Cách dùng: Pha nước uống hoặc  trộn vào thức ăn.
+Liều dùng:&lt;/div&gt;&lt;div&gt;- Gà, vịt, ngan, ngỗng: pha 3 g/ lít nước uống hoặc trộn 3 g/ kg thức ăn.&lt;/div&gt;&lt;div&gt;- Lợn, trâu, bò: Pha 100 g/ 50 lít nước uống hoặc trộn 100 g/ 50-60 kg thức ăn.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1149,7 +1094,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1184,24 +1129,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thành phần:
-Bromhexin HCl: 1g
-Tá dược vừa đủ: 100 g
-Công dụng:
-- Trị bệnh phế quản phổi cấp và mãn tính liên quan đến tiết chất nhầy trên bê, lợn, gia cầm, chó, mèo.
-- Giảm ho, tiêu đờm, chống co thắt phế quản trong các bệnh viêm phế quản, viêm thanh quản truyền nhiễm, viêm phổi, suyễn, sổ mũi truyền nhiễm, CRD, CCRD.
-Liều lượng và cách dùng:
-Pha nước uống hoặc trộn với thức ăn dùng liên tục 3 – 5 ngày theo liều:
-– Gà, vịt, ngan, cút: 1g/10 – 12 kg TT hoặc 1 g/1 -2 lít nước uống hoặc trộn 1 g/2 kg thức ăn.
-– Lợn và gia súc khác: 1 g/18 – 20 kg thể trọng.
-Chống chỉ định:
-- Động vật mẫn cảm với thành phần của thuốc. 
-- Không sử dụng cho động vật 4 tuần trước và trong khi sinh sản. 
-- Không dùng cho động vật lấy trứng và sữa. 
-Thời gian ngưng sử dụng thuốc:
-Thịt và nội tạng: 7 ngày
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Bromhexin HCl: 1g&lt;/div&gt;&lt;div&gt;Tá dược vừa đủ: 100 g&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Trị bệnh phế quản phổi cấp và mãn tính liên quan đến tiết chất nhầy trên bê, lợn, gia cầm, chó, mèo.&lt;/div&gt;&lt;div&gt;- Giảm ho, tiêu đờm, chống co thắt phế quản trong các bệnh viêm phế quản, viêm thanh quản truyền nhiễm, viêm phổi, suyễn, sổ mũi truyền nhiễm, CRD, CCRD.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Pha nước uống hoặc trộn với thức ăn dùng liên tục 3 – 5 ngày theo liều:&lt;/div&gt;&lt;div&gt;– Gà, vịt, ngan, cút: 1g/10 – 12 kg TT hoặc 1 g/1 -2 lít nước uống hoặc trộn 1 g/2 kg thức ăn.&lt;/div&gt;&lt;div&gt;– Lợn và gia súc khác: 1 g/18 – 20 kg thể trọng.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Động vật mẫn cảm với thành phần của thuốc.&lt;/div&gt;&lt;div&gt;- Không sử dụng cho động vật 4 tuần trước và trong khi sinh sản.&lt;/div&gt;&lt;div&gt;- Không dùng cho động vật lấy trứng và sữa.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Thịt và nội tạng: 7 ngày&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1319,7 +1247,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1330,268 +1258,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ENDIA</t>
+          <t>BV - BIOTIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bộ sản phẩm</t>
+          <t>Thức ăn bổ sung</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Điều trị tiêu chảy</t>
+          <t>Tăng trưởng &amp; chất lượng trứng</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tiêm 1 mũi duy nhất, đặc trị tiêu chảy do nhiễm khuẩn</t>
+          <t>Tăng trọng, mọc lông, chống cắn mổ, chống còi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thành phần:
-Trong 100ml có chứa:
-- Enrofloxacin: 10 g
-- Dung môi vừa đủ: 100 ml
-Công dụng:
-Trị nhiễm trùng đường tiêu hóa, hô hấp, niệu sinh dục, nhiễm khuẩn huyết, nhiễm trùng da, vết thương trên trâu, bò, bê, nghé, dê, cừu, lợn.
-Chỉ định của BSTY:
-Đặc trị viêm ruột, tiêu chảy do E.coli, Salmonella, viêm phổi, viêm vú, viêm tử cung, viêm khớp, hen khẹc trên gia súc, gia cầm.
-Liều lượng và cách dùng:
-Tiêm mũi duy nhất, tiêm bắp hoặc tiêm dưới da
-- Gà, vịt, ngan, cút: 1ml/6-8kg TT.
-- Lợn: 1ml/8-12kg TT.
-- Lợn con: 1ml/6-7kg TT.
-- Trâu, bò, dê, cừu: 1ml/15-20kg TT.
-Trường hợp bệnh nặng: Tiêm nhắc lại sau 36-48h.
-Chống chỉ định:
-Không sử dụng cho vật nuôi mẫn cảm với các thành phần của thuốc.
-Thời gian ngưng sử dụng thuốc:
-- Trâu, bò, bê, nghé, dê, cừu: 21 ngày.
-- Lợn: 14 ngày.
-- Gia cầm: 7 ngày.
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;- Vitamin B1 (min): 10000mg&lt;/div&gt;&lt;div&gt;- Vitamin B2(min): 3000 mg&lt;/div&gt;&lt;div&gt;- Vitamin B6(min): 300 mg&lt;/div&gt;&lt;div&gt;- Biotin (min): 450 mg&lt;/div&gt;&lt;div&gt;- Kẽm (min- max): 70-150 mg&lt;/div&gt;&lt;div&gt;- Lysine (min): 2000 mg&lt;/div&gt;&lt;div&gt;- Vitamin D3 (min): 2000 mg&lt;/div&gt;&lt;div&gt;- Canxi (min-max): 2000-3500mg&lt;/div&gt;&lt;div&gt;- Tá dược vừa đủ: 1000 g&lt;/div&gt;&lt;div&gt;Thành phần bổ sung hỗn hợp 10 lại enzyme hữu hiệu: Phytase, amylase, xylanase, protease, mannanase, cellulose, pectinase, B- Glucannsase, a- Galactosidase, lipase. 
+Sản phẩm không chứa chất kháng sinh, hoocmon và các chất độc hại.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Kích thích mọc lông, chống cắn mổ&lt;/div&gt;&lt;div&gt;- Bổ sung vitamin thiết yếu và khoáng chất vi lượng cho gia cầm&lt;/div&gt;&lt;div&gt;- Vỗ béo, chống còi, tăng sản lượng thịt, tăng số lượng và chất lượng trứng.&lt;/div&gt;&lt;div&gt;- Tạo màu vàng đẹp cho lòng đỏ trứng&lt;/div&gt;&lt;div&gt;- Nâng cao năng suất cho gia cầm sinh sản&lt;/div&gt;&lt;div&gt;- Trứng to, vỏ dày, tỷ lệ đẻ cao, kéo dài.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Pha nước uống hoặc trộn thức ăn.&lt;/div&gt;&lt;div&gt;- Gà, vịt, lợn con: 100 g/ 50-100 kg thức ăn&lt;/div&gt;&lt;div&gt;- Lợn nái, lợn con: 20g/20-30 kg thức ăn.&lt;/div&gt;&lt;div&gt;- Trâu, bò, dê, cừu, bê, nghé: 20 g/ 50 kg thức ăn.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ c.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Điều trị nhiễm khuẩn nặng;Tiêu chảy cấp;Phòng kế phát sau tiêu chảy</t>
+          <t>Mọc lông;Chống còi;Tăng chất lượng trứng</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>280000</v>
+        <v>190000</v>
       </c>
       <c r="J6" t="n">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Lọ tiêm</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Gia súc</t>
+          <t>Gia cầm, gia súc</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>Trong 100ml có chứa:
-Enrofloxacin 10 g
-Dung môi vừa đủ 100 ml</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tiêm mũi duy nhất, tiêm bắp hoặc tiêm dưới da
-- Gà, vịt, ngan, cút: 1ml/6-8kg TT.
-- Lợn: 1ml/8-12kg TT.
-- Lợn con: 1ml/6-7kg TT.
-- Trâu, bò, dê, cừu: 1ml/15-20kg TT.
-Trường hợp bệnh nặng: Tiêm nhắc lại sau 36-48h.</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>5 ngày</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-      <c r="X6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>33</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>/images/product-edb21e58-1753327191.jpg</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>endia,tiêu chảy,thuốc tiêm,viêm tử cung,nhiễm khuẩn</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>endia,đặc trị tiêu chảy,thuốc tiêm nhiễm khuẩn,heo</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>ENDIA - Khắc tinh tiêu chảy, hiệu quả cao với 1 mũi tiêm duy nhất</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BV - BIOTIN</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Thức ăn bổ sung</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tăng trưởng &amp; chất lượng trứng</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tăng trọng, mọc lông, chống cắn mổ, chống còi</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thành phần:
-- Vitamin B1 (min): 10000mg 
-- Vitamin B2(min): 3000 mg
-- Vitamin B6(min): 300 mg
-- Biotin (min): 450 mg
-- Kẽm (min- max): 70-150 mg
-- Lysine (min): 2000 mg
-- Vitamin D3 (min): 2000 mg
-- Canxi (min-max): 2000-3500mg 
-- Tá dược vừa đủ: 1000 g 
-Thành phần bổ sung hỗn hợp 10 lại enzyme hữu hiệu: Phytase, amylase, xylanase, protease, mannanase, cellulose, pectinase, B- Glucannsase, a- Galactosidase, lipase. 
-Sản phẩm không chứa chất kháng sinh, hoocmon và các chất độc hại. 
-Công dụng:
-- Kích thích mọc lông, chống cắn mổ
-- Bổ sung vitamin thiết yếu và khoáng chất vi lượng cho gia cầm
-- Vỗ béo, chống còi, tăng sản lượng thịt, tăng số lượng và chất lượng trứng. 
-- Tạo màu vàng đẹp cho lòng đỏ trứng
-- Nâng cao năng suất cho gia cầm sinh sản 
-- Trứng to, vỏ dày, tỷ lệ đẻ cao, kéo dài.
-Liều lượng và cách dùng:
-- Pha nước uống hoặc trộn thức ăn.
-- Gà, vịt, lợn con: 100 g/ 50-100 kg thức ăn 
-- Lợn nái, lợn con: 20g/20-30 kg thức ăn. 
-- Trâu, bò, dê, cừu, bê, nghé: 20 g/ 50 kg thức ăn. 
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ c. </t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Mọc lông;Chống còi;Tăng chất lượng trứng</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>190000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Gói</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Gia cầm, gia súc</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
         <is>
           <t>Vitamin B1 (min) 10000mg 
 Vitamin B2(min) 3000 mg
@@ -1606,7 +1331,7 @@
 Sản phẩm không chứa chất kháng sinh, hoocmon và các chất độc hại.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Pha nước uống hoặc trộn thức ăn.
 Gà, vịt, lợn con: 100 g/ 50-100 kg thức ăn 
@@ -1614,178 +1339,148 @@
 Trâu, bò, dê, cừu, bê, nghé: 20 g/ 50 kg thức ăn.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0 ngày</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ c.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>24 tháng</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Halife</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="b">
-        <v>0</v>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="b">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
         <v>1</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z6" t="n">
         <v>250</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA6" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB6" t="n">
         <v>21</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>/images/product-1cef78f3-1753327271.jpg</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>biotin,tăng trọng,mọc lông,vỏ trứng đỏ,chống mổ</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>bv biotin,tăng sản lượng,chống cắn mổ,tăng chất lượng trứng</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>BV-BIOTIN - Siêu tăng trọng, chống cắn mổ, tăng chất lượng trứng rõ rệt</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="7">
+      <c r="A7" t="n">
         <v>12</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>AN THAI BỔ NÁI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Thức ăn bổ sung</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hỗ trợ sinh sản</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Tăng lượng sữa, dưỡng nái, ngừa sảy thai, thai khỏe, con sai</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Thành phần:
-Trong 1000g có chứa:
-- Zn (Min - max): 1600 -1800 mg/kg
-- Fe (Min - max): 3000 - 5000 mg/kg
-- Lysine (min): 15000 mg/kg
-- Vitamin A (min): 2.500.000 IU/kg
-- Vitamin D (min): 1.000.000 IU/kg
-- Vitamin E (min): 620 mg/kg
-- Biotin (min): 400 mg/kg
-- Senlen (min - max): 38-54 mg/kg
-- Tá dược vừa đủ: 1000g
-Thành phần nguyên liệu: 
-- Bổ sung vi sinh vật có lợi: lactobacillus; sacharomyces; bacillus subtilis
-- Bổ sung hỗn hợp 10 loại enzyme : Bổ sung hỗn hợp 10 enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)
-- Bổ sung thành phần thảo dược: Mộc hương, hoài sơn, ý dĩ, thần khúc, sơn tra.
-Công dụng:
-Bổ sung probiotic,acid amin, hỗn hợp vitamin và khoáng thiết yếu cho vật nuôi, công thức đặc biệt bổ sung dưỡng chất cho đối tượng con nái để: 
-* Tăng cường sức khỏe, Tăng tỷ lệ đậu thai và tỷ lệ đẻ, Tăng số con trong lứa.
-* Đối với nái chửa: Cân bằng dinh dưỡng, bào thai phát triển tốt hơn, đẻ dễ dàng hơn.
-* Đối với nái chờ phối: Sử dụng sản phẩm thường xuyên giúp rút ngắn thời gian lên giống sau cai sữa, động dục mạnh hơn.
-* Phòng nứt móng, sừng hóa da.
-* Khung xương phát triển mạnh, hạn chế bại liệt.
-Liều lượng và cách dùng:
-CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.
-LIỀU DÙNG: 
-- Nái chửa : 1kg trộn với 400 – 600 kg thức ăn hỗn hợp.
-- Nái hậu bị và nái chờ phối : 1kg trộn với 1.000 kg thức ăn hỗn hợp.
-- Hòa nước: 1g/2-3 lít nước uống.
-Lưu ý : Có thể dùng chung với kháng sinh để phòng bệnh.
-Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Trong 1000g có chứa:&lt;/div&gt;&lt;div&gt;- Zn (Min - max): 1600 -1800 mg/kg&lt;/div&gt;&lt;div&gt;- Fe (Min - max): 3000 - 5000 mg/kg&lt;/div&gt;&lt;div&gt;- Lysine (min): 15000 mg/kg&lt;/div&gt;&lt;div&gt;- Vitamin A (min): 2.500.000 IU/kg&lt;/div&gt;&lt;div&gt;- Vitamin D (min): 1.000.000 IU/kg&lt;/div&gt;&lt;div&gt;- Vitamin E (min): 620 mg/kg&lt;/div&gt;&lt;div&gt;- Biotin (min): 400 mg/kg&lt;/div&gt;&lt;div&gt;- Senlen (min - max): 38-54 mg/kg&lt;/div&gt;&lt;div&gt;- Tá dược vừa đủ: 1000g&lt;/div&gt;&lt;div&gt;Thành phần nguyên liệu:&lt;/div&gt;&lt;div&gt;- Bổ sung vi sinh vật có lợi: lactobacillus; sacharomyces; bacillus subtilis&lt;/div&gt;&lt;div&gt;- Bổ sung hỗn hợp 10 loại enzyme: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)&lt;/div&gt;&lt;div&gt;- Bổ sung thành phần thảo dược: Mộc hương, hoài sơn, ý dĩ, thần khúc, sơn tra.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Bổ sung probiotic,acid amin, hỗn hợp vitamin và khoáng thiết yếu cho vật nuôi, công thức đặc biệt bổ sung dưỡng chất cho đối tượng con nái để:&lt;/div&gt;&lt;div&gt;- Tăng cường sức khỏe, Tăng tỷ lệ đậu thai và tỷ lệ đẻ, Tăng số con trong lứa.&lt;/div&gt;&lt;div&gt;- Đối với nái chửa: Cân bằng dinh dưỡng, bào thai phát triển tốt hơn, đẻ dễ dàng hơn.&lt;/div&gt;&lt;div&gt;- Đối với nái chờ phối: Sử dụng sản phẩm thường xuyên giúp rút ngắn thời gian lên giống sau cai sữa, động dục mạnh hơn.&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Phòng nứt móng, sừng hóa da.&lt;/div&gt;&lt;div&gt;- Khung xương phát triển mạnh, hạn chế bại liệt.&amp;nbsp;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.&amp;nbsp;&lt;/div&gt;&lt;div&gt;LIỀU DÙNG:&lt;/div&gt;&lt;div&gt;- Nái chửa : 1kg trộn với 400 – 600 kg thức ăn hỗn hợp.&lt;/div&gt;&lt;div&gt;- Nái hậu bị và nái chờ phối : 1kg trộn với 1.000 kg thức ăn hỗn hợp.&lt;/div&gt;&lt;div&gt;- Hòa nước: 1g/2-3 lít nước uống.&lt;/div&gt;&lt;div&gt;Lưu ý : Có thể dùng chung với kháng sinh để phòng bệnh.
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Bổ sung khoáng &amp; vitamin sinh sản;Ngừa sảy thai;Dưỡng nái</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
         <v>220000</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J7" t="n">
         <v>290000</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Gói</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Heo nái</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Trong 1000g có chứa:
 Zn (Min - max) 1600 -1800 mg/kg
@@ -1803,7 +1498,7 @@
 Bổ sung thành phần thảo dược: Mộc hương, hoài sơn, ý dĩ, thần khúc, sơn tra.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.
 LIỀU DÙNG: 
@@ -1814,6 +1509,163 @@
 Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0 ngày</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halife</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>/images/product-99896a92-1753321132.jpg</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>an thai bổ nái,dưỡng nái,tăng sữa,tăng đậu thai,sinh sản</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>an thai bổ nái,dưỡng nái,ngừa sảy thai,vitamin sinh sản</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>AN THAI BỔ NÁI - Dưỡng nái, bổ sung khoáng chất và vitamin giúp mẹ khỏe, con sai, ngừa sảy thai</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADE ĐẠM SỮA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Thức ăn bổ sung</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tăng trọng &amp; sức đề kháng</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tăng trọng, tăng cơ, bung lông, giảm chi phí nuôi</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Trong 1000g có chứa:&lt;/div&gt;&lt;div&gt;- Protein thô* min: 5%&lt;/div&gt;&lt;div&gt;- Vitamin A(min): 800.000 IU/k&lt;/div&gt;&lt;div&gt;- Vitamin D (min): 160.000 IU/kg&lt;/div&gt;&lt;div&gt;- Vitamin E (min): 1800 mg/kg&lt;/div&gt;&lt;div&gt;- Vitamin B1 (min): 1200 mg/kg&lt;/div&gt;&lt;div&gt;- Vitamin B2 (min) 800 mg/kg&lt;/div&gt;&lt;div&gt;- Vitamin B6 (min): 1000 mg/kg&lt;/div&gt;&lt;div&gt;- Amylase (min): 2400 IU/kg&lt;/div&gt;&lt;div&gt;- Protease (min): 4000 IU/kg&lt;/div&gt;&lt;div&gt;- Lysine (min): 8000 mg/kg&lt;/div&gt;&lt;div&gt;- Methionine (min): 6000 mg/kg&lt;/div&gt;&lt;div&gt;- Sorbitol (min): 5000 mg/kg&lt;/div&gt;&lt;div&gt;- Tá dược vừa đủ: 1000g&lt;/div&gt;&lt;div&gt;Thành phần nguyên liệu:&lt;/div&gt;&lt;div&gt;Bổ sung hỗn hợp 10 enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Công thức dinh dưỡng hoàn chỉnh, hàm lượng đạm cao, hiệu quả vỗ béo nhanh, xuất chuồng sớm, hạn chế dùng kháng sinh trong chăn nuôi gia súc gia cầm.&lt;/div&gt;&lt;div&gt;- Giải pháp nâng cao hiệu quả chăn nuôi. Bổ sung vitamin, acid amin và enzyme cho vật nuôi trong các trường hợp cần thiết.&lt;/div&gt;&lt;div&gt;- Bổ sung protein 1 cách cân đối. Có thể bổ sung thay thế cho sữa mẹ khi nái mất sữa trong những ngày ốm kém do vận chuyển xa.&lt;/div&gt;&lt;div&gt;- Kích thích tính thèm ăn và tăng cường tiêu hóa, hấp thu, cải thiện hiệu quả thức ăn.&lt;/div&gt;&lt;div&gt;- Giảm tỷ lệ chết, tăng cường sức đề kháng, tăng cường khả năng miễn dịch cho vật nuôi.&lt;/div&gt;&lt;div&gt;- Giảm tiêu tốn thức ăn, rút ngắn thời gian nuôi.&lt;/div&gt;&lt;div&gt;- Vật nuôi lớn nhanh, khỏe mạnh, lợn ích chăn nuôi vượt trội.&lt;/div&gt;&lt;div&gt;- Vật nuôi lớn nhanh, khoẻ mạnh, lợi ích tăng trưởng chăn nuôi vượt trội.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;CÁCH DÙNG:&lt;/div&gt;&lt;div&gt;Hòa nước uống hoặc trộn với thức ăn.&lt;/div&gt;&lt;div&gt;LIỀU DÙNG:&lt;/div&gt;&lt;div&gt;- Hòa nước uống: 1g/ 2-3 lít nước.&lt;/div&gt;&lt;div&gt;- Trộn thức ăn: cho ăn giai đoạn trước khi xuất. 
+Gia cầm: 1kg/ 500 - 1000 kg thức ăn.
+Gia súc: 1kg/ 300 - 500 kg thức ăn.
+Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tăng trọng;Tăng cơ;Hạn chế kháng sinh</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1g/1kg thức ăn, dùng trong các giai đoạn cần tăng trưởng nhanh hoặc sau cai sữa</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>280000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>350000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Gói</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Gia súc, Gia cầm</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Vitamin A, D, E, protein sữa</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1g/1kg thức ăn</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>0 ngày</t>
@@ -1821,7 +1673,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
+          <t>Để nơi thoáng mát</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1839,9 +1691,13 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>VN-2024-ADESUA</t>
+        </is>
+      </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
@@ -1850,43 +1706,47 @@
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>/images/product-99896a92-1753321132.jpg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr"/>
+          <t>/images/product-d9255d53-1753328021.jpg</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>/images/ade-dam-sua.png;/images/gallery-ade-dam-sua.png</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>an thai bổ nái,dưỡng nái,tăng sữa,tăng đậu thai,sinh sản</t>
+          <t>đạm sữa,tăng trọng,tăng cơ,vật nuôi lớn nhanh</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>an thai bổ nái,dưỡng nái,ngừa sảy thai,vitamin sinh sản</t>
+          <t>ade đạm sữa,tăng cân,tăng cơ,protein,không kháng sinh</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>AN THAI BỔ NÁI - Dưỡng nái, bổ sung khoáng chất và vitamin giúp mẹ khỏe, con sai, ngừa sảy thai</t>
+          <t>ADE ĐẠM SỮA - Tăng trọng, đạm cao, tăng cơ nhanh, giảm tiêu tốn thức ăn</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1897,11 +1757,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADE ĐẠM SỮA</t>
+          <t>OCTA-NEW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1911,107 +1771,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tăng trọng &amp; sức đề kháng</t>
+          <t>Viêm tử cung &amp; sinh dục</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tăng trọng, tăng cơ, bung lông, giảm chi phí nuôi</t>
+          <t>Đặc trị viêm tử cung, viêm vú, mất sữa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thành phần:
-Trong 1000g có chứa:
-- Protein thô* min: 5%
-- Vitamin A(min): 800.000 IU/kg
-- Vitamin D (min): 160.000 IU/kg
-- Vitamin E (min): 1800 mg/kg
-- Vitamin B1 (min): 1200 mg/kg
-- Vitamin B2 (min) 800 mg/kg
-- Vitamin B6 (min): 1000 mg/kg
-- Amylase (min): 2400 IU/kg
-- Protease (min): 4000 IU/kg
-- Lysine (min): 8000 mg/kg
-- Methionine (min): 6000 mg/kg
-- Sorbitol (min): 5000 mg/kg
-- Tá dược vừa đủ: 1000g 
-Thành phần nguyên liệu: 
-Bổ sung hỗn hợp 10 loại enzyme : Bổ sung hỗn hợp 10 enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)
-Công dụng:
-* Công thức dinh dưỡng hoàn chỉnh, hàm lượng đạm cao, hiệu quả vỗ béo nhanh, xuất chuồng sớm, hạn chế dùng kháng sinh trong chăn nuôi gia súc gia cầm.
-* Giải pháp nâng cao hiệu quả chăn nuôi. Bổ sung vitamin, acid amin và enzyme cho vật nuôi trong các trường hợp cần thiết.
-* Bổ sung protein 1 cách cân đối. Có thể bổ sung thay thế cho sữa mẹ khi nái mất sữa trong những ngày ốm kém do vận chuyển xa.
-* Kích thích tính thèm ăn và tăng cường tiêu hóa, hấp thu, cải thiện hiệu quả thức ăn.
-* Giảm tỷ lệ chết, tăng cường sức đề kháng, tăng cường khả năng miễn dịch cho vật nuôi.
-* Giảm tiêu tốn thức ăn, rút ngắn thời gian nuôi.
-* Vật nuôi lớn nhanh, khỏe mạnh, lợn ích chăn nuôi vượt trội.
-* Vật nuôi lớn nhanh, khoẻ mạnh, lợi ích tăng trưởng chăn nuôi vượt trội.
-Liều lượng và cách dùng:
-CÁCH DÙNG: Hòa nước uống hoặc trộn với thức ăn.
-LIỀU DÙNG: 
-* Hòa nước uống: 1g/ 2-3 lít nước.
-* Trộn thức ăn: cho ăn giai đoạn trước khi xuất. 
-Gia cầm: 1kg/ 500 - 1000 kg thức ăn.
-Gia súc: 1kg/ 300 - 500 kg thức ăn.
-Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.
-</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;- Oxytetracycline: 30g&lt;/div&gt;&lt;div&gt;- Flunixin: 2g&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ: 100ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Đặc trị các bệnh đường tiết niệu, sinh dục như: viêm tử cung trước và sau khi sinh, viêm vú, mất sữa (MMA), ở gia súc, heo.&lt;/div&gt;&lt;div&gt;- Điều trị các bệnh nhiễm trùng đường hô hấp: viêm phổi, CRD, CCRD; các bệnh đường tiêu hoá: viêm ruột, viêm ruột tiêu chảy...&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Tiêm bắp sâu 1 liều duy nhất.&lt;/div&gt;&lt;div&gt;- Liều lượng: 1 ml / 10 kg thể trọng/ngày.&lt;/div&gt;&lt;div&gt;- Thể tích tối đa trên mỗi vị trí tiêm: 15 ml.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.&lt;/div&gt;&lt;div&gt;- Không sử dụng cho động vật bị suy gan, thận.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Lấy thịt:
+Trâu, bò, dê, cừu, heo: 35 ngày.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tăng trọng;Tăng cơ;Hạn chế kháng sinh</t>
+          <t>Viêm tử cung;Mất sữa;Viêm phổi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1g/1kg thức ăn, dùng trong các giai đoạn cần tăng trưởng nhanh hoặc sau cai sữa</t>
+          <t>Tiêm 1ml/10-15kg thể trọng trong 3-5 ngày hoặc theo chỉ định</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>280000</v>
+        <v>220000</v>
       </c>
       <c r="J9" t="n">
-        <v>350000</v>
+        <v>320000</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>Lọ tiêm</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gia súc, Gia cầm</t>
+          <t>Gia súc</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Vitamin A, D, E, protein sữa</t>
+          <t>Oxytetracycline, multivitamin</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1g/1kg thức ăn</t>
+          <t>1ml/10-15kg thể trọng</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0 ngày</t>
+          <t>7 ngày</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Để nơi thoáng mát</t>
+          <t>Nơi mát, tránh ánh nắng</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2031,60 +1856,60 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>VN-2024-ADESUA</t>
+          <t>VN-2024-OCTANEW</t>
         </is>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>/images/product-d9255d53-1753328021.jpg</t>
+          <t>/images/product-29a966ac-1753332407.jpg</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>/images/ade-dam-sua.png;/images/gallery-ade-dam-sua.png</t>
+          <t>/images/octa-new.png;/images/gallery-octa-new.png</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>đạm sữa,tăng trọng,tăng cơ,vật nuôi lớn nhanh</t>
+          <t>octa-new,viêm tử cung,mất sữa,sinh dục,crd</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ade đạm sữa,tăng cân,tăng cơ,protein,không kháng sinh</t>
+          <t>octa-new,đặc trị viêm tử cung,sản khoa,mất sữa</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>ADE ĐẠM SỮA - Tăng trọng, đạm cao, tăng cơ nhanh, giảm tiêu tốn thức ăn</t>
+          <t>OCTA-NEW - Thuốc tiêm trị viêm tử cung, mất sữa và viêm hô hấp</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2095,11 +1920,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OCTA-NEW</t>
+          <t>WINTOSAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2109,50 +1934,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Viêm tử cung &amp; sinh dục</t>
+          <t>Hồi sức &amp; trao đổi chất</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Đặc trị viêm tử cung, viêm vú, mất sữa</t>
+          <t>Tăng trao đổi chất, hồi sức, chống suy nhược</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thành phần:
-- Oxytetracycline: 30g
-- Flunixin: 2g 
-- Dung môi vừa đủ: 100ml
-Công dụng:
-- Đặc trị các bệnh đường tiết niệu, sinh dục như: viêm tử cung trước và sau khi sinh, viêm vú, mất sữa (MMA), ở gia súc, heo. 
-- Điều trị các bệnh nhiễm trùng đường hô hấp: viêm phổi, CRD, CCRD; các bệnh đường tiêu hoá: viêm ruột, viêm ruột tiêu chảy...
-Liều lượng và cách dùng:
-- Tiêm bắp sâu 1 liều duy nhất. 
-- Liều lượng: 1 ml / 10 kg thể trọng/ngày. 
-- Thể tích tối đa trên mỗi vị trí tiêm: 15 ml.
-Chống chỉ định:
-- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc. 
-- Không sử dụng cho động vật bị suy gan, thận.
-Thời gian ngưng sử dụng thuốc:
-Lấy thịt:
-Trâu, bò, dê, cừu, heo: 35 ngày.</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;- Butaphosphan: 10 g&lt;/div&gt;&lt;div&gt;- Vitamin B12: 5mg&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ: 100 ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Điều trị các rối loạn chuyển hoá cấp và mãn tính. Rối loạn phát triển dinh dưỡng ở gia súc non, kích thích trao đổi chất, tăng trọng lớn nhanh, ngừa stress. Hỗ trợ điều trị bệnh ghép, E.coli, CRD, heo tai xanh.&lt;/div&gt;&lt;div&gt;- Tăng cường khả năng sinh sản, tăng tỉ lệ trứng ở gà, vịt, cút, kích sữa ở gia súc, hỗ trợ trị bệnh hậu sản, phòng sốt sữa, bại liệt sau khi sinh, hỗ trợ điều trị vô sinh.&lt;/div&gt;&lt;div&gt;- Điều trị các trường hợp kiệt sức, giảm sức đề kháng, suy nhược, thiếu máu, hồi phục sức khoẻ nhanh, phòng chống còi xương duy dinh dưỡng. Tăng chuyển hoá, giúp heo con đồng đều, cứng cáp, chống còi cọc.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Dùng tiêm dưới da, tiêm bắp hoặc tiêm tĩnh mạch.&lt;/div&gt;&lt;div&gt;- Trâu, bò, ngựa: 10-25 ml/con (Chỉ dùng tiêm tĩnh mạch).&lt;/div&gt;&lt;div&gt;- Ngựa non, bê, nghé: 5-12 ml/con (Chỉ dùng tiêm tĩnh mạch).&lt;/div&gt;&lt;div&gt;- Lợn, cừu, dê: 2,5-10 ml/con.&lt;/div&gt;&lt;div&gt;- Lợn con: 1-2.5 ml/con (Chỉ tiêm dưới da)&lt;/div&gt;&lt;div&gt;&amp;nbsp;- Gia cầm: 0.5-1 ml/con. 
+ Lặp lại điều trị trong 1-2 tuần (nếu cần).&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Viêm tử cung;Mất sữa;Viêm phổi</t>
+          <t>Hồi sức;Tăng trao đổi chất;Chống suy nhược</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tiêm 1ml/10-15kg thể trọng trong 3-5 ngày hoặc theo chỉ định</t>
+          <t>Tiêm 1ml/10kg thể trọng trong 3 ngày liên tiếp hoặc theo hướng dẫn</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>220000</v>
+        <v>320000</v>
       </c>
       <c r="J10" t="n">
-        <v>320000</v>
+        <v>400000</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2174,22 +1984,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Oxytetracycline, multivitamin</t>
+          <t>Vitamin B-complex, Glucose, Electrolytes</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1ml/10-15kg thể trọng</t>
+          <t>1ml/10kg thể trọng</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7 ngày</t>
+          <t>0 ngày</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Nơi mát, tránh ánh nắng</t>
+          <t>Nơi mát, kín nắp</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2209,60 +2019,60 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>VN-2024-OCTANEW</t>
+          <t>VN-2024-WINTOSAL</t>
         </is>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>/images/product-29a966ac-1753332407.jpg</t>
+          <t>/images/product-214a5212-1753332114.jpg</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>/images/octa-new.png;/images/gallery-octa-new.png</t>
+          <t>/images/wintosal.png;/images/gallery-wintosal.png</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>octa-new,viêm tử cung,mất sữa,sinh dục,crd</t>
+          <t>wintosal,hồi sức,tăng trao đổi chất,giảm suy nhược,sinh sản</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>octa-new,đặc trị viêm tử cung,sản khoa,mất sữa</t>
+          <t>wintosal,tăng trao đổi chất,chống stress,thúc đẻ</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>OCTA-NEW - Thuốc tiêm trị viêm tử cung, mất sữa và viêm hô hấp</t>
+          <t>WINTOSAL - Bổ trợ chuyển hóa, sinh sản, hồi sức nhanh chóng</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2273,282 +2083,74 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WINTOSAL</t>
+          <t>GOOD SET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thức ăn bổ sung</t>
+          <t>Bộ sản phẩm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hồi sức &amp; trao đổi chất</t>
+          <t>Cử lý tối ưu</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tăng trao đổi chất, hồi sức, chống suy nhược</t>
+          <t>Xử lý tối ưu hô hấp, viêm phổi trên vật nuôi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thành phần:
-- Butaphosphan: 10 g
-- Vitamin B12: 5mg
-- Dung môi vừa đủ: 100 ml
-Công dụng:
-- Điều trị các rối loạn chuyển hoá cấp và mãn tính. Rối loạn phát triển dinh dưỡng ở gia súc non, kích thích trao đổi chất, tăng trọng lớn nhanh, ngừa stress. Hỗ trợ điều trị bệnh ghép, E.coli, CRD, heo tai xanh.
-- Tăng cường khả năng sinh sản, tăng tỉ lệ trứng ở gà, vịt, cút, kích sữa ở gia súc, hỗ trợ trị bệnh hậu sản, phòng sốt sữa, bại liệt sau khi sinh, hỗ trợ điều trị vô sinh.
-- Điều trị các trường hợp kiệt sức, giảm sức đề kháng, suy nhược, thiếu máu, hồi phục sức khoẻ nhanh, phòng chống còi xương duy dinh dưỡng. Tăng chuyển hoá, giúp heo con đồng đều, cứng cáp, chống còi cọc.
-Liều lượng và cách dùng:
-Duùng tiêm dưới da, tiêm bắp hoặc tiêm tĩnh mạch. 
-- Trâu, bò, ngựa: 10-25 ml/con (Chỉ dùng tiêm tĩnh mạch).
-- Ngựa non, bê, nghé: 5-12 ml/con (Chỉ dùng tiêm tĩnh mạch).
-- Lợn, cừu, dê: 2,5-10 ml/con.
-- Lợn con: 1-2.5 ml/con (Chỉ tiêm dưới da).
-- Gia cầm: 0.5-1 ml/con. 
- Lặp lại điều trị trong 1-2 tuần (nếu cần).
-Chống chỉ định:
-Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.
-Bảo quản:
-Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Trong 100ml có chứa:&lt;/div&gt;&lt;div&gt;- Florfenicol: 45g&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ: 100ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Công thức, tá dược, dung môi dung hòa đặc biệt, giúp bộ đôi sản phẩm tiêu diệt hầy hết các loại vi khuẩn gây ra bệnh đường hô hấp cho gia súc
+Heo:&lt;/div&gt;&lt;div&gt;- Phòng và trị bệnh viêm đường hô hấp phức hợp (heo hắt hơi từng hồi, chảy nước mũi, ho, khó thở, thở nhanh và nhiều, heo há hốc mồm để thở)&lt;/div&gt;&lt;div&gt;- Phòng và trị bệnh viêm phổi, suyễn, tụ huyết trùng, viêm phổi - màng Phổi, bệnh Glaser, viêm teo xoang mũi&lt;/div&gt;&lt;div&gt;- Phòng các bệnh bội nhiễm và kế phát khi heo bệnh tai xanh (PRRS) và lở mồm long móng (FMD)&amp;nbsp;&lt;/div&gt;&lt;div&gt;Trâu bò, dê, cừu:&lt;/div&gt;&lt;div&gt;- Trị các bệnh đường hô hấp như viêm phổi, tụ huyết trùng, viêm hô hấp phức hợp,&lt;/div&gt;&lt;div&gt;- Viêm kết giác mạc,&lt;/div&gt;&lt;div&gt;- Phòng các bệnh bội nhiễm và kế phát khi trâu bò, dê, cừu bệnh lở mồm long móng. bệnh thối móng&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÁCH DÙNG VÀ LIỀU DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;CÁCH DÙNG:&lt;/div&gt;&lt;div&gt;Tiêm bắp hoặc tiêm dưới da một liều duy nhất&lt;/div&gt;&lt;div&gt;LIỀU DÙNG:&lt;/div&gt;&lt;div&gt;Lấy 1ml ANPHA NEW + 1ml WINFLO LA lắc đều. Sau đó lấy 2 ml hỗn hợp dung dịch kháng sinh tiêm cho:&lt;/div&gt;&lt;div&gt;- HEO: 2ml/15-20 kg thể trọng đối với bệnh nặng và 2ml/25-30 kg thể trọng đối với bệnh nhẹ. Tiêm bắp 1 liều duy nhất&lt;/div&gt;&lt;div&gt;- TRÂU BÒ: 2ml/40kg thể trọng&lt;/div&gt;&lt;div&gt;- DÊ, CỪU: 2ml /40 kg thể trọng&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỈ ĐỊNH CỦA BSTY:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Đặc trị hen suyễn, viêm phổi, phó thương hàn, E.coli, lepto, viêm phổi hóa mủ, viêm phổi dính sườn, tụ huyết trùng, hồng lỵ, E.coli, sưng phù đầu, viêm ruột ỉa chảy, viêm vú, viêm tử cung, nhiễm trùng huyết sau sinh, sốt bỏ ăn, bệnh kế phát tai xanh, sốt đỏ (PRRS) do nhiều loại vi khuẩn bội nhiễm, tiêu chảy phân xanh, phân trắng ở gà, vịt.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Không sử dụng cho vật nuôi mẫn cảm với các thành phần của thuốc.&lt;/div&gt;&lt;div&gt;- Không sử dụng cho động vật lấy sữa thương phẩm và trong thời gian cho con bú&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;46 ngày trước khi giết mổ.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hồi sức;Tăng trao đổi chất;Chống suy nhược</t>
+          <t>Phòng và trị viêm đường hô hấp;Phòng bệnh kế phát;Tối ưu phổi và miễn dịch</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tiêm 1ml/10kg thể trọng trong 3 ngày liên tiếp hoặc theo hướng dẫn</t>
+          <t>Tiêm bắp hoặc tiêm dưới da một liều duy nhất</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>320000</v>
+        <v>550000</v>
       </c>
       <c r="J11" t="n">
-        <v>400000</v>
+        <v>550000</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Lọ tiêm</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>2 chai</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Gia súc</t>
+          <t>Gia súc, Gia cầm</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Vitamin B-complex, Glucose, Electrolytes</t>
+          <t>WINFLO LA, ANPHA NEW</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>1ml/10kg thể trọng</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0 ngày</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Nơi mát, kín nắp</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Halife</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>VN-2024-WINTOSAL</t>
-        </is>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>180</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>/images/product-214a5212-1753332114.jpg</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>/images/wintosal.png;/images/gallery-wintosal.png</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>wintosal,hồi sức,tăng trao đổi chất,giảm suy nhược,sinh sản</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>wintosal,tăng trao đổi chất,chống stress,thúc đẻ</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>WINTOSAL - Bổ trợ chuyển hóa, sinh sản, hồi sức nhanh chóng</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>2024-02-09</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GOOD SET</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bộ sản phẩm</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Cử lý tối ưu</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Xử lý tối ưu hô hấp, viêm phổi trên vật nuôi</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>THÀNH PHẦN:
-Trong 100ml có chứa:
-- Florfenicol: 45g
-- Dung môi vừa đủ: 100ml
-Công dụng:
-Công thức, tá dược, dung môi dung hòa đặc biệt, giúp bộ đôi sản phẩm tiêu diệt hầy hết các loại vi khuẩn gây ra bệnh đường hô hấp cho gia súc
-Heo:
-* Phòng và trị bệnh viêm đường hô hấp phức hợp (heo hắt hơi từng hồi, chảy nước mũi, ho, khó thở, thở nhanh và nhiều, heo há hốc mồm để thở)
-* Phòng và trị bệnh viêm phổi, suyễn, tụ huyết trùng, viêm phổi - màng hổi, bệnh Glaser, viêm teo xoang mũi
-* Phòng các bệnh bội nhiễm và kế phát khi heo bệnh tai xanh (PRRS) và lở mồm long móng (FMD)
-Trâu bò, dê, cừu:
-* Trị các bệnh đường hô hấp như viêm phổi, tụ huyết trùng, viêm hô hấp phức hợp, 
-* Viêm kết giác mạc,
-* Phòng các bệnh bội nhiễm và kế phát khi trâu bò, dê, cừu bệnh lở mồm long móng. bệnh thối móng
-Cách dùng và liều dùng:
-CÁCH DÙNG: Tiêm bắp hoặc tiêm dưới da một liều duy nhất
-LIỀU DÙNG: Lấy 1ml ANPHA NEW + 1ml WINFLO LA lắc đều. Sau đó lấy 2 ml hỗn hợp dung dịch kháng sinh tiêm cho:
-HEO: 2ml/15-20 kg thể trọng đối với bệnh nặng và 2ml/25-30 kg thể trọng đối với bệnh nhẹ. Tiêm bắp 1 liều duy nhất
-TRÂU BÒ: 2ml/40kg thể trọng
-DÊ, CỪU: 2ml /40 kg thể trọng
-Chỉ định của BSTY:
-Đặc trị hen suyễn, viêm phổi, phó thương hàn, E.coli, lepto, viêm phổi hóa mủ, viêm phổi dính sườn, tụ huyết trùng, hồng lỵ, E.coli, sưng phù đầu, viêm ruột ỉa chảy, viêm vú, viêm tử cung, nhiễm trùng huyết sau sinh, sốt bỏ ăn, bệnh kế phát tai xanh, sốt đỏ (PRRS) do nhiều loại vi khuẩn bội nhiễm, tiêu chảy phân xanh, phân trắng ở gà, vịt.
-Chống chỉ định:
-- Không sử dụng cho vật nuôi mẫn cảm với các thành phần của thuốc.
-- Không sử dụng cho động vật lấy sữa thương phẩm và trong thời gian cho con bú
-Thời gian ngừng sử dụng thuốc:
-46 ngày trước khi giết mổ.
-Bảo quản:
-Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới 30°C.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Phòng và trị viêm đường hô hấp;Phòng bệnh kế phát;Tối ưu phổi và miễn dịch</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Tiêm bắp hoặc tiêm dưới da một liều duy nhất</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>550000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>550000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2 chai</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Gia súc, Gia cầm</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>WINFLO LA, ANPHA NEW</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
         <is>
           <t>Lấy 1ml ANPHA NEW + 1ml WINFLO LA lắc đều. Sau đó lấy 2 ml hỗn hợp dung dịch kháng sinh tiêm cho:
 - HEO: 2ml/15-20 kg thể trọng đối với bệnh nặng và 2ml/25-30 kg thể trọng đối với bệnh nhẹ. Tiêm bắp 1 liều duy nhất
@@ -2556,14 +2158,164 @@
 - DÊ, CỪU: 2ml /40 kg thể trọng</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>7 ngày</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Khô thoáng, tránh ánh nắng</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halife</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>VN-2024-GOODSET</t>
+        </is>
+      </c>
+      <c r="W11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>/images/product-d23b9ee5-1753321141.jpg</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>/images/product-bad4093e-1752512778.png;/images/product-ce5b7ccf-1752512778.png;/images/product-955251ab-1752512778.png</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>good set,hô hấp,viêm phổi,heo tai xanh,lở mồm long móng</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>good set,viêm phổi,hô hấp,halife</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>GOOD SET - Bộ đôi xử lý tối ưu các bệnh viêm phổi, hô hấp, phòng bệnh kế phát</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cefket 515</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Đặc trị viêm vú, viêm tử cung, viêm khớp, viêm móng</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;- Ceftiofur (dạng hydroclorid): 5 g&lt;/div&gt;&lt;div&gt;- Ketoprofen: 5 g&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ: 100 ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Trị hội chứng MMA (viêm tử cung, viêm vú, mất sữa)&lt;/div&gt;&lt;div&gt;- Trị viêm phổi, viêm phế quản, viêm phổi dính sườn, hen suyễn, tụ huyết trùng&lt;/div&gt;&lt;div&gt;- Trị tiêu chảy do E.coli, Salmonella, sưng phù đầu, viêm ruột tiêu chảy, phân trắng lợn con, viêm da, Lepto, nhiễm trùng huyết, sốt bỏ ăn không rõ nguyên nhân. Bệnh kế phát do LMLM, TNRS, VDNC.&lt;/div&gt;&lt;div&gt;- Trị viêm khớp, thối móng, viêm vú, viêm tử cung ở trâu bò&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Tiêm bắp 1 liều duy nhất. Lắc kĩ trước khi sử dụng.&lt;/div&gt;&lt;div&gt;- Lấy 1ml/ 50 kg thể trọng mỗi lần tiêm. Dùng từ 3-5 ngày liên tục.&lt;/div&gt;&lt;div&gt;- Không tiêm quá 16 ml tại bất kì vị trí tiêm bắp nào. Các lần tiếp theo phải được tiêm ở vị trí khác.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.&lt;/div&gt;&lt;div&gt;- Không sử dụng cho động vật suy gan, suy thận.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Lấy thịt và nội tạng: 08 ngày&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong bao bì kín, nơi khô ráo thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>480000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>550000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Gia súc, gia cầm</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Ceftiofur (dạng hydroclorid).……5g
+Ketoprofen…………………...….....15g
+Dung môi vừa đủ……………...100ml</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tiêm bắp 1 liều duy nhất. Lắc kĩ trước khi sử dụng.
+Lấy 1ml/ 50 kg thể trọng mỗi lần tiêm. Dùng từ 3-5 ngày liên tục.
+Không tiêm quá 16 ml tại bất kì vị trí tiêm bắp nào. Các lần tiếp theo phải được tiêm ở vị trí khác.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Khô thoáng, tránh ánh nắng</t>
+          <t>Trong bao bì kín, nơi khô ráo thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2573,7 +2325,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Halife</t>
+          <t>HALIFE Việt Nhật</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2583,60 +2335,44 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>VN-2024-GOODSET</t>
+          <t>WIN-136</t>
         </is>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>5</v>
       </c>
       <c r="AB12" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>/images/product-d23b9ee5-1753321141.jpg</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>/images/product-bad4093e-1752512778.png;/images/product-ce5b7ccf-1752512778.png;/images/product-955251ab-1752512778.png</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>good set,hô hấp,viêm phổi,heo tai xanh,lở mồm long móng</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>good set,viêm phổi,hô hấp,halife</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>GOOD SET - Bộ đôi xử lý tối ưu các bệnh viêm phổi, hô hấp, phòng bệnh kế phát</t>
-        </is>
-      </c>
+          <t>/images/product-7b55c739-1761021747.jpg</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2647,11 +2383,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cefket 1015</t>
+          <t>ENDIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2662,40 +2398,21 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Đặc trị viêm vú, viêm tử cung, viêm khớp, viêm móng</t>
+          <t>KHẮC TINH TIÊU CHẢY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thành phần:
-- Ceftiofur (dạng hydroclorid): 5 g
-- Ketoprofen: 5 g
-- Dung môi vừa đủ: 100 ml
-Công dụng:
-- Trị hội chứng MMA (viêm tử cung, viêm vú, mất sữa)
-- Trị viêm phổi, viêm phế quản, viêm phổi dính sườn, hen suyễn, tụ huyết trùng
-- Trị tiêu chảy do E.coli, Salmonella, sưng phù đầu, viêm ruột tiêu chảy, phân trắng lợn con, viêm da, Lepto, nhiễm trùng huyết, sốt bỏ ăn không rõ nguyên nhân. Bệnh kế phát do LMLM, TNRS, VDNC.
-- Trị viêm khớp, thối móng, viêm vú, viêm tử cung ở trâu bò
-Liều lượng và cách dùng:
-- Tiêm bắp 1 liều duy nhất. Lắc kĩ trước khi sử dụng.
-- Lấy 1ml/ 50 kg thể trọng mỗi lần tiêm. Dùng từ 3-5 ngày liên tục.
-- Không tiêm quá 16 ml tại bất kì vị trí tiêm bắp nào. Các lần tiếp theo phải được tiêm ở vị trí khác.
-Chống chỉ định:
-- Không sử dụng cho động vật mẫn cảm với các thành phần của thuốc.
-- Không sử dụng cho động vật suy gan, suy thận.
-Thời gian ngưng sử dụng thuốc:
-Lấy thịt và nội tạng: 08 ngày
-Bảo quản:
-Trong bao bì kín, nơi khô ráo thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C</t>
+          <t>KHẮC TINH TIÊU CHẢY</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>480000</v>
+        <v>280000</v>
       </c>
       <c r="J13" t="n">
-        <v>550000</v>
+        <v>350000</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2710,31 +2427,11 @@
           <t>100ml</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Gia súc, gia cầm</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Ceftiofur (dạng hydroclorid).……5g
-Ketoprofen…………………...….....15g
-Dung môi vừa đủ……………...100ml</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Tiêm bắp 1 liều duy nhất. Lắc kĩ trước khi sử dụng.
-Lấy 1ml/ 50 kg thể trọng mỗi lần tiêm. Dùng từ 3-5 ngày liên tục.
-Không tiêm quá 16 ml tại bất kì vị trí tiêm bắp nào. Các lần tiếp theo phải được tiêm ở vị trí khác.</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Trong bao bì kín, nơi khô ráo thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>24 tháng</t>
@@ -2750,13 +2447,9 @@
           <t>Việt Nam</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>WIN-136</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="b">
         <v>0</v>
@@ -2765,17 +2458,17 @@
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>/images/product-cf73eee0-1753322027.jpg</t>
+          <t>/images/product-4d1df8d6-1753332777.jpg</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2789,7 +2482,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2800,36 +2493,36 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ENDIA</t>
+          <t>DEEP MAX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thuốc kháng sinh</t>
+          <t>Vitamin &amp; khoáng chất</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KHẮC TINH TIÊU CHẢY</t>
+          <t>Siêu đề kháng, siêu miễn dịch, bảo vệ vật nuôi toàn diện</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KHẮC TINH TIÊU CHẢY</t>
+          <t>&lt;div&gt;&lt;div style=""&gt;&lt;b&gt;ỨC CHẾ SỰ NHÂN LÊN CỦA VIRUS&amp;nbsp;&lt;/b&gt;&lt;b&gt;DỊCH TẢ HEO CHÂU PHI&lt;/b&gt;&lt;/div&gt;&lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;KÍCH HOẠT HỆ MIỄN DỊCH CHỦ ĐỘNG&lt;/b&gt;&lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;PHÒNG VÀ HỖ TRỢ ĐIỀU TRỊ:&lt;/b&gt;&lt;/div&gt;&lt;div style=""&gt;- Dịch tả heo châu Phi&lt;/div&gt;&lt;div style=""&gt;- Lở mồm long móng, tai xanh&lt;/div&gt;&lt;div style=""&gt;- Virus trên gia cầm&lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong 1000g có chứa:&lt;/div&gt;&lt;div&gt;Beta-glucan tổng số* min...... 10000 mg&lt;/div&gt;&lt;div&gt;Vitamin C* min..................... 20000 mg&lt;/div&gt;&lt;div&gt;Methionine* min..................... 6000 mg&lt;/div&gt;&lt;div&gt;Lysine tổng số* min.............. 20000 mg&lt;/div&gt;&lt;div&gt;Tá dược vừa đủ......................... 1000 g&amp;nbsp;&lt;/div&gt;&lt;div&gt;Sản phẩm không chứa kháng sinh, hoocmon.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Ức chế sự nhân lên của virus dịch tả heo Châu Phi.&lt;/div&gt;&lt;div&gt;- Kích thích hệ miễn dịch, tăng cường hoạt động của các đại thực bào, tiêu diệt các mầm bệnh xâm nhập từ bên - ngoài.&lt;/div&gt;&lt;div&gt;- Tăng cường sức đề kháng cho vật nuôi để chống chịu bệnh tật, tăng cường chức năng gan, thận.&lt;/div&gt;&lt;div&gt;- Cung cấp vitamin, acid amin. Vật nuôi lớn nhanh khỏe mạnh.&lt;/div&gt;&lt;div&gt;- Phòng chống stress do yếu tố ngoại cảnh, chủng ngừa vaccine, nhiễm độc, nôn mửa, xuất huyết nội tạng, khi vận chuyển, nhập hoặc tách đàn.&lt;/div&gt;&lt;div&gt;- Giảm FCR, kích thích tiêu hóa hấp thu và phòng bệnh đường ruột.&lt;/div&gt;&lt;div&gt;- Đặc biệt hỗ trợ trong phòng và điều trị bệnh trên gia súc: Dịch tả heo châu phi, tai xanh, lở mồm long móng, sốt đỏ trên heo, New, Gumboro và các bệnh virus trên gia cầm.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;!--StartFragment--&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;CÁCH DÙNG &amp;amp; LIỀU LƯỢNG:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;Trộn vào thức ăn hoặc pha vào nước uống:&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;Hoà 1g/2-3 lít nước hoặc 1g/10-20kg thể trọng/ngày.&amp;nbsp;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;Trộn thức ăn: 1-2kg/1000kg thức ăn.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br&gt;&lt;/div&gt;&lt;!--EndFragment--&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong bao bì khô ráo, thoáng mát, tránh ánh nắng trực tiếp. Nhiệt độ dưới 30°C.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>280000</v>
+        <v>650000</v>
       </c>
       <c r="J14" t="n">
-        <v>350000</v>
+        <v>690000</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2841,121 +2534,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>1KG</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>24 tháng</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>HALIFE Việt Nhật</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>/images/product-4d1df8d6-1753332777.jpg</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>27</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GLUCAN MAX</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Vitamin &amp; khoáng chất</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Siêu đề kháng, siêu miễn dịch, bảo vệ vật nuôi toàn diện</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Siêu đề kháng, siêu miễn dịch, bảo vệ vật nuôi toàn diện</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>450000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>480000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hộp</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1KG</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Trong 1000g có chứa:
 Beta-glucan tổng số* min.....................................10000mg
@@ -2966,17 +2549,148 @@
 Sản phẩm không chứa kháng sinh, hoocmon.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Trộn vào thức ăn hoặc pha vào nước uống:
 Hoà 1g/2-3 lít nước hoặc 1g/10-20kg thể trọng/ ngày 
 Trộn thức ăn: 1-2kg/1000kg thức ăn.</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Trong bao bì khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>/images/product-3d338f16-1755664946.jpg</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BEST PHAGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bộ sản phẩm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GIẢI PHÁP VÀNG THAY THẾ KHÁNG SINH
+CẢI THIỆN SỨC KHOẺ ĐƯỜNG RUỘT- NÂNG CAO KHẢ NĂNG MIỄN DỊCH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Bacillus spp(min): 1x107&lt;/div&gt;&lt;div&gt;Dung môi vừa đủ: 1000ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Xử lí hoàn toàn các vi khuẩn gây bệnh như Salmonella spp, Escherichia coli và C.perfringens trên gia súc, gia cầm.&lt;/div&gt;&lt;div&gt;- Cải thiện sức khoẻ đường ruột, sản sinh vi khuẩn có lợi, hấp thu thức ăn triệt để, cải thiện FCR&lt;/div&gt;&lt;div&gt;- Sử dụng tất cả các giai đoạn của vật nuôi.&lt;/div&gt;&lt;div&gt;- Kết hợp với sản phẩm Boost phage giúp tăng năng suất, hiệu quả chăn nuôi, sớm xuất bán&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Lắc đều trước khi sử dụng.&lt;/div&gt;&lt;div&gt;- Phòng bệnh: 1ml pha với 2 lít nước, dùng cho 30 kg thể trọng vật nuôi.&lt;/div&gt;&lt;div&gt;- Vật nuôi giai đoạn úm: Thay thế kháng sinh, dùng liên tục từ 5- 7 ngày khi bắt đầu giai đoạn úm. Sau đó, sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục từ 2-3 ngày.&lt;/div&gt;&lt;div&gt;- Gia súc, gia cầm: Sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục 2-3 ngày.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>489000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>550000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>250ML</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Gia súc, gia cầm</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Bacillus spp(min) 1x107
+Dung môi vừa đủ  1000ml</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lắc đều trước khi sử dụng. 
+Phòng bệnh: 1ml pha với 2 lít nước, dùng cho 30 kg thể trọng vật nuôi.
+Vật nuôi giai đoạn úm: Thay thế kháng sinh, dùng liên tục từ 5- 7 ngày khi bắt đầu giai đoạn úm. Sau đó, sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục từ 2-3 ngày.  
+Gia súc, gia cầm: Sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục 2-3 ngày.</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Trong bao bì khô ráo, thoáng mát, tránh ánh sáng trực tiếp. Nhiệt độ dưới 30°C.</t>
+          <t>Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -3008,14 +2722,14 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>/images/product-e50da535-1753340636.jpg</t>
+          <t>/images/product-e2bcbad7-1753437123.jpg</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -3024,12 +2738,12 @@
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3040,51 +2754,36 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BEST PHAGE</t>
+          <t>NANO BẠC AG+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bộ sản phẩm</t>
+          <t>Thuốc kháng sinh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GIẢI PHÁP VÀNG THAY THẾ KHÁNG SINH
-CẢI THIỆN SỨC KHOẺ ĐƯỜNG RUỘT- NÂNG CAO KHẢ NĂNG MIỄN DỊCH</t>
+          <t>SÁT TRÙNG THẾ HỆ MỚI SIÊU MẠNH, SIÊU BÁM DÍNH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thành phần:
-Bacillus spp(min): 1x107
-Dung môi vừa đủ: 1000ml 
-Công dụng:
-- Xử lí hoàn toàn các vi khuẩn gây bệnh như Salmonella spp, Escherichia coli và C.perfringens trên gia súc, gia cầm.
-- Cải thiện sức khoẻ đường ruột, sản sinh vi khuẩn có lợi, hấp thu thức ăn triệt để, cải thiện FCR
-- Sử dụng tất cả các giai đoạn của vật nuôi. 
-- Kết hợp với sản phẩm Boost phage giúp tăng năng suất, hiệu quả chăn nuôi, sớm xuất bán
-Liều lượng và cách dùng:
-Lắc đều trước khi sử dụng. 
-- Phòng bệnh: 1ml pha với 2 lít nước, dùng cho 30 kg thể trọng vật nuôi.
-- Vật nuôi giai đoạn úm: Thay thế kháng sinh, dùng liên tục từ 5- 7 ngày khi bắt đầu giai đoạn úm. Sau đó, sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục từ 2-3 ngày.  
-- Gia súc, gia cầm: Sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục 2-3 ngày. 
-Bảo quản:
-Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C. </t>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;(trong 1000g có chứa)&lt;div&gt;- Silver 360 mg&lt;/div&gt;&lt;div&gt;- Hydrogen Peroxide 500 g&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ 1000 ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;* Công dụng với các loại virus, vi khuẩn, nấm bệnh:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Virus dịch tả lợn châu Phi (ASFV): làm biến tính vỏ protein và vật chất di truyền của virus, tiêu diệt nhanh virus trong môi trường.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;- Virus tai xanh (PRRS): gây mất ổn định màng bao virus, ức chế nhân lên giúp giảm lây lan trong trại nuôi.&lt;/div&gt;&lt;div&gt;- Virus lở mồm long móng (FMD): tấn công lớp vỏ protein và RNA, giúp vô hiệu hóa virus nhanh chóng.&lt;/div&gt;&lt;div&gt;- Virus cúm gia cầm (H5N1, H9N2,...): làm mất hoạt tính virus, hỗ trợ khống chế dịch bệnh hiệu quả.&lt;/div&gt;&lt;div&gt;- Vi khuẩn: tác động mạnh lên màng tế bào vi khuẩn, phá hủy cấu trúc và tiêu diệt vi khuẩn, kể cả chủng kháng kháng sinh.&lt;/div&gt;&lt;div&gt;- Nấm bệnh (Candida, Aspergillus...): Phá hủy màng tế bào nấm, ức chế sinh trưởng bào tử, ngăn ngừa nhiễm nấm và nấm mốc.&lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;* Khử trùng môi trường &amp;amp; nguồn nước:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Khử trùng chuồng trại, sàn nền, không khí: Nano bạc và hydrogen peroxide tạo hiệu ứng oxy hóa mạnh, giúp tiêu diệt mầm bệnh trong không khí và bề mặt&lt;/div&gt;&lt;div&gt;- Khử trùng nguồn nước uống, nước thải, nước ao hồ: Diệt virus, vi khuẩn và nấm trong nước, làm sạch nước dùng cho chăn nuôi hoặc thủy sản.&lt;/div&gt;&lt;div&gt;- Không gây tồn dư độc hại: Sau khi phản ứng, hydrogen peroxide phân hủy thành nước và oxy, Nano bạc ở nồng độ thấp vẫn an toàn với vật nuôi.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CƠ CHẾ KẾT HỢP:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Nano bạc: phá màng tế bào, làm bất hoạt enzyme của vi sinh vật.&lt;/div&gt;&lt;div&gt;- Hydrogen peroxide: giải phóng oxy hoạt tính, phá vỡ cấu trúc tế bào/ virus.&lt;/div&gt;&lt;div&gt;- Tăng cường lẫn nhau, giúp diệt mầm bệnh nhanh, rộng phổ và kéo dài hiệu quả.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;ƯU ĐIỂM VƯỢT TRỘI:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Không gây kháng thuốc.&lt;/div&gt;&lt;div&gt;- Không tồn dư độc hại.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Khử trùng định kỳ: 1 lít pha 300 - 400 lít nước sạch, phun 400 - 500 m2, lưu lại trong 3 - 5 giờ. Sau đó làm sạch bằng nước. Khi có nguy cơ dịch, áp lực mầm bệnh cao: tăng liều lên gấp đôi.&lt;/div&gt;&lt;div&gt;- Tẩy uế chuồng trại sau khi bị nhiễm bệnh do virus dịch tả heo châu phi , tai xanh, LMLM, cúm gia cầm ...: 1 lít/ 50 - 100 lít nước sạch, phun 100 - 140 m2 nền chuồng.&lt;/div&gt;&lt;div&gt;- Khử trùng nước uống: 1 lít/ 2000 lít nước uống.&lt;/div&gt;&lt;div&gt;- Vệ sinh và khử trùng hệ thống nước uống trong chuồng trống: tỷ lệ 1 lít/ 300 lít nước để trong 90 phút đến 5 giờ. Sau đó làm sạch bằng nước. Đảm bảo đủ thông gió.&lt;/div&gt;&lt;div&gt;- Dung dịch tắm móng: tỷ lệ 1 lít/ 300 lít nước cho trâu, bò, lợn, dê cừu đi qua. 1 lần/ tuần.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỐNG CHỈ ĐỊNH:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Không sử dụng cho vật nuôi mẫn cảm với bất cứ thành phần của thuốc.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;0 ngày.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.&amp;nbsp;&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>489000</v>
+        <v>260000</v>
       </c>
       <c r="J16" t="n">
-        <v>550000</v>
+        <v>260000</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -3094,36 +2793,12 @@
           <t>hộp</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>250ML</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Gia súc, gia cầm</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Bacillus spp(min) 1x107
-Dung môi vừa đủ  1000ml</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Lắc đều trước khi sử dụng. 
-Phòng bệnh: 1ml pha với 2 lít nước, dùng cho 30 kg thể trọng vật nuôi.
-Vật nuôi giai đoạn úm: Thay thế kháng sinh, dùng liên tục từ 5- 7 ngày khi bắt đầu giai đoạn úm. Sau đó, sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục từ 2-3 ngày.  
-Gia súc, gia cầm: Sử dụng định kì mỗi 5-7 ngày, mỗi đợt dùng liên tục 2-3 ngày.</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Trong bao bì kín, nơi khô ráo, thoáng mát, tránh ánh nắng trực tiếp, nhiệt độ dưới 30 độ C.</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>24 tháng</t>
@@ -3141,7 +2816,7 @@
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="b">
         <v>0</v>
@@ -3153,14 +2828,14 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>/images/product-e2bcbad7-1753437123.jpg</t>
+          <t>/images/product-fa8a0bf4-1754731087.jpg</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -3169,15 +2844,1019 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CEFGEN PRO MAX-LA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Đặc trị VIÊM PHỔI, PHỔI DÍNH SƯỜN, HEN SUYỄN, VIÊM VÚ, VIÊM TỬ CUNG, TỤ HUYẾT TRÙNG, E.COLI, TIÊU CHẢY, SƯNG PHÙ ĐẦU, BỆNH KẾ PHÁT CỦA LMLM VÀ TAI XANH (SỐT ĐỎ, PRRS).</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>&lt;table border="0" cellpadding="0" cellspacing="0" width="589" style="width: 442pt;"&gt;
+ &lt;colgroup&gt;&lt;col width="589" style="mso-width-source:userset;mso-width-alt:18858;width:442pt"&gt;
+ &lt;/colgroup&gt;&lt;tbody&gt;&lt;tr height="169" style="mso-height-source:userset;height:127.5pt"&gt;
+&lt;!--StartFragment--&gt;
+  &lt;td height="169" class="xl65" width="589" style="height:127.5pt;width:442pt"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;THÀNH PHẦN:&lt;/span&gt;&lt;br&gt;Trong
+  1000ml có chứa:&lt;br&gt;
+    Ceftiofur hydroclorid................................10 g&lt;br&gt;
+    Gentamycin sulfate....................................5 g&lt;br&gt;
+    Dung môi vừa đủ.................................100 ml&lt;br&gt;&lt;br&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;br&gt;&lt;table border="0" cellpadding="0" cellspacing="0" width="589" style="width: 442pt;"&gt;
+ &lt;colgroup&gt;&lt;col width="589" style="mso-width-source:userset;mso-width-alt:18858;width:442pt"&gt;
+ &lt;/colgroup&gt;&lt;tbody&gt;&lt;tr height="124" style="mso-height-source:userset;height:93.75pt"&gt;
+&lt;!--StartFragment--&gt;
+  &lt;td height="124" class="xl68" width="589" style="height:93.75pt;width:442pt"&gt;Đặc
+  trị viêm màng phổi, phổi dính sườn, hen suyễn viêm vú, viêm tử cung MMA, viêm
+  dạ con, tụ huyết trùng, phó thương hàn, E.coli sưng phù đầu, viêm ruột tiêu
+  chảy, phân trắng lợn con, viêm da, viêm đa khớp, nhiễm trùng huyết, kế phát
+  do LMLM, kế phát của hội chứng rối loạn hô hấp và sinh sản (tai xanh, sốt đỏ,
+  prrs)... Các vi khuẩn Gram (+) và Gram (-) nhạy cảm với Ceftiofur.&lt;br&gt;&lt;br&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/span&gt;&lt;br&gt;&lt;table border="0" cellpadding="0" cellspacing="0" width="589" style="width: 442pt;"&gt;
+ &lt;colgroup&gt;&lt;col width="589" style="mso-width-source:userset;mso-width-alt:18858;width:442pt"&gt;
+ &lt;/colgroup&gt;&lt;tbody&gt;&lt;tr height="61" style="mso-height-source:userset;height:46.5pt"&gt;
+&lt;!--StartFragment--&gt;
+  &lt;td height="61" class="xl67" width="589" style="height:46.5pt;width:442pt"&gt;Tiêm bắp
+  thịt hoặc dưới da. Một mũi tiêm tác dụng kéo dài 72 - 96h&lt;br&gt;
+    - Lợn: 1 ml/ 20 - 30 kg thể trọng/ ngày.&lt;br&gt;
+    - Trâu, bò, dê: 1 ml/ 45 - 60 kg thể trọng/ ngày. &lt;br&gt;
+    - Lợn con, chó, mèo: 1 ml/ 12 - 18 kg thể trọng/ ngày.&lt;br&gt;&lt;br&gt;&lt;b&gt;BẢO QUẢN:&lt;/b&gt;&lt;br&gt;&lt;table border="0" cellpadding="0" cellspacing="0" width="589" style="width: 442pt;"&gt;
+ &lt;colgroup&gt;&lt;col width="589" style="mso-width-source:userset;mso-width-alt:18858;width:442pt"&gt;
+ &lt;/colgroup&gt;&lt;tbody&gt;&lt;tr height="32" style="mso-height-source:userset;height:24.0pt"&gt;
+&lt;!--StartFragment--&gt;
+  &lt;td height="32" class="xl67" width="589" style="height:24.0pt;width:442pt"&gt;Trong
+  bao bì kín, nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ dưới
+  30°C.&lt;/td&gt;
+&lt;!--EndFragment--&gt;
+ &lt;/tr&gt;
+&lt;/tbody&gt;&lt;/table&gt;&lt;/td&gt;
+&lt;!--EndFragment--&gt;
+ &lt;/tr&gt;
+&lt;/tbody&gt;&lt;/table&gt;&lt;/td&gt;
+&lt;!--EndFragment--&gt;
+ &lt;/tr&gt;
+&lt;/tbody&gt;&lt;/table&gt;&lt;/td&gt;
+&lt;!--EndFragment--&gt;
+ &lt;/tr&gt;
+&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>/images/product-4637092a-1755764646.jpg</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>31</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A80</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ĐẶC TRỊ MYCOPLASMA SUIS
+THÍCH HỢP TRÊN HEO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>&lt;!--StartFragment--&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;THÀNH PHẦN:&lt;/span&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Oxytetracyclin .......................................... 30 g&amp;nbsp;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Flunixin .......................................................... 2 g&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Dung môi vừa đủ .................................. 100 ml&lt;/div&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;CÔNG DỤNG:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Đặc trị các bệnh đường tiết niệu, sinh dục như: viêm tử cung trước và sau khi sinh, viêm vú, mất sữa (MMA), ở gia súc, heo.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Điều trị các bệnh nhiễm trùng, đường hô hấp: viêm phổi, CRD, CCRD; các bệnh đường tiêu hóa: viêm ruột, viêm ruột tiêu chảy,...&lt;/div&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;CHỈ ĐỊNH CỦA BSTY:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;Điều trị Mycoplasma suis và bệnh ghép Mycoplasma suis&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Tiêm bắp sau 1 liều duy nhất.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Liều lượng: 1ml/ 10kg thể trọng/ ngày.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Thể tích tối đa trên mỗi vị trí tiêm: 15ml.&lt;/div&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;Lấy thịt: Trâu, bỏ, bê, cừu, heo: 35 ngày.&lt;/div&gt;&lt;!--EndFragment--&gt;</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>228000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>/images/product-283d105b-1761013738.png</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TAM ĐA PLUS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BỘ 3 SIÊU CẤP
+CHỐNG NHỜN HOÀN HẢO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>&lt;!--StartFragment--&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;THÀNH PHẦN:&lt;/span&gt;&lt;/div&gt;&lt;span style="color: rgb(55, 65, 81); font-size: 18px;"&gt;BỘ CÓ 3 SẢN PHẨM:&lt;/span&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;ul&gt;&lt;li&gt;1. TẤN CÔNG (CEFTRI MAX): 30 g&lt;/li&gt;&lt;/ul&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;br&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;2. TIÊU DIỆT (SPEC-TOL): 250ml&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&amp;nbsp; &amp;nbsp;Trong 100ml có chứa:&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&amp;nbsp; &amp;nbsp;Lincomycin HCl......................&amp;nbsp; 5g&amp;nbsp;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&amp;nbsp; &amp;nbsp;Spectinomycin HCl…............. 10g&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&amp;nbsp; &amp;nbsp;Dung môi vừa đủ.............. 100ml&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br&gt;&lt;/div&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;3. CỘNG HƯỜNG ( ALNAGIN 50 ): 250ml&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&amp;nbsp; &amp;nbsp;Trong 100ml có chứa:&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&amp;nbsp; &amp;nbsp;Analgin….............................. 50g&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&amp;nbsp; &amp;nbsp;Dung môi vừa đủ............... 100ml&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;CÔNG DỤNG:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;Điều trị hiệu quả bệnh nhiễm trùng Hô hấp, CRD, Hen ORT và các biến chứng của bệnh (C.CRD), bệnh Thương hàn, Tụ huyết trùng, Viêm khớp và Bại huyết, E.coli, khẹc vịt trên gia cầm, thủy cầm.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;span style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; font-weight: bolder;"&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/span&gt;&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ; color: rgb(55, 65, 81); font-size: 18px;"&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Tiêm bắp hoặc tiêm dưới da.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Rút 100 ml từ chai số 2 SPEC TOL đổ vào chai số 1 CEFTRI MAX&amp;nbsp; lắc kỹ tan hoàn toàn, đổ sang chai khô, sạch thể tích 500 ml, đổ tiếp số lượng chai&amp;nbsp; số&amp;nbsp; 2 SPEC TOL còn lại, đổ tiếp chai số 3 ANAGIN 50 lắc kỹ cho đồng nhất hoàn toàn. Tiêm bắp hoặc tiêm dưới da.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;- Liều Chung: 1ml/2 kg TT. Ngày tiêm 1-2 lần. Điều trị liên tục ít nhất 3-5 ngày.&lt;/div&gt;&lt;div style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw-hue-rotate: ; --tw-invert: ; --tw-saturate: ; --tw-sepia: ; --tw-drop-shadow: ; --tw-backdrop-blur: ; --tw-backdrop-brightness: ; --tw-backdrop-contrast: ; --tw-backdrop-grayscale: ; --tw-backdrop-hue-rotate: ; --tw-backdrop-invert: ; --tw-backdrop-opacity: ; --tw-backdrop-saturate: ; --tw-backdrop-sepia: ; --tw-contain-size: ; --tw-contain-layout: ; --tw-contain-paint: ; --tw-contain-style: ;"&gt;&lt;br style="--tw-scale-x: 1; --tw-scale-y: 1; --tw-pan-x: ; --tw-pan-y: ; --tw-pinch-zoom: ; --tw-scroll-snap-strictness: proximity; --tw-gradient-from-position: ; --tw-gradient-via-position: ; --tw-gradient-to-position: ; --tw-ordinal: ; --tw-slashed-zero: ; --tw-numeric-figure: ; --tw-numeric-spacing: ; --tw-numeric-fraction: ; --tw-ring-inset: ; --tw-ring-offset-width: 0px; --tw-ring-offset-color: #fff; --tw-ring-color: rgb(0 35 145 / .5); --tw-ring-offset-shadow: 0 0 #0000; --tw-ring-shadow: 0 0 #0000; --tw-shadow: 0 0 #0000; --tw-shadow-colored: 0 0 #0000; --tw-blur: ; --tw-brightness: ; --tw-contrast: ; --tw-grayscale: ; --tw</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>950000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>980000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>/images/product-b6838e0e-1758590690.jpg</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A80 BỔ HUYẾT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Thức ăn bổ sung</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TĂNG CƯỜNG CHỨC NĂNG GAN, BỔ GAN LỢI MẬT
+TĂNG CƯỜNG CHUYỂN HÓA, TRAO ĐỔI CHẤT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;&lt;div&gt;- Sorbitol*(min) ............................ 300.000 mg&lt;/div&gt;&lt;div&gt;- L – lysine (min).................................. 3000 mg&lt;/div&gt;&lt;div&gt;- DL - DL - Methionine min* (min)...... 800 mg&lt;/div&gt;&lt;div&gt;- Thiamin*(min).................................... 1000 mg&lt;/div&gt;&lt;div&gt;- Inositol*(min)..................................... 1000 mg&lt;/div&gt;&lt;div&gt;- Kẽm (Zn) (min - max) ......... 1500 - 3000 mg&lt;/div&gt;&lt;div&gt;- Potassium (Kali) (min - max)......... 5,000 mg&lt;/div&gt;&lt;div&gt;- Chất mang vừa đủ ........................... 1,000 g&lt;/div&gt;&lt;div&gt;Sản phẩm không chứa kháng sinh, hoocmon.&lt;/div&gt;&lt;div&gt;Bổ sung thảo dược astiso, betain, acid amin tổng hợp và vitamin tổng hợp.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;- Bổ sung các axit amin và vitamin cần thiết và các dưỡng chất quan trọng, giúp vật nuôi sinh trưởng và phát triển khỏe mạnh.&lt;/div&gt;&lt;div&gt;- Giải độc nhanh, phục hồi chức năng gan, tái tạo tế bào gan, ngăn ngừa các bệnh về gan như vàng gan, sưng gan, đỏ gan, teo gan.&lt;/div&gt;&lt;div&gt;- Tăng cường sức đề kháng, tăng cường miễn dịch, hạn chế bệnh kế phát.&lt;/div&gt;&lt;div&gt;- Phòng chống stress do ngoại cảnh, chủng ngừa vaccine, vận chuyển, tách đàn… hỗ trợ hiệu quả trong phòng bệnh thường gặp như: Gumboro, CRD trên gia cầm, tiêu chảy…&lt;/div&gt;&lt;div&gt;- Cải thiện FCR. Vật nuôi lớn nhanh, khỏe mạnh, ít bệnh. Góp phần giảm thiểu ô nhiễm môi trường nuôi.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;CÁCH DÙNG:&lt;/div&gt;&lt;div&gt;Hòa nước uống hoặc trộn với thức ăn.&lt;/div&gt;&lt;div&gt;LIỀU DÙNG:&amp;nbsp;&lt;/div&gt;&lt;div&gt;Gia súc: 1g/4-5 lít nước hoặc 20 - 25kg thể trọng.&lt;/div&gt;&lt;div&gt;Gia cầm: 1g/3-4 lít nước hoặc 15 - 20kg thể trọng.&lt;/div&gt;&lt;div&gt;Trường hợp vật nuôi mệt mỏi hoặc cần giải độc cấp, cần thiết có thể sử dụng liều lượng gấp đôi.&lt;/div&gt;&lt;div&gt;Nên sử dụng thường xuyên trong suôt vụ nuôi để bảo vệ gan, kích thích miễn dịch và tăng cường tiêu hóa.&lt;/div&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>488000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>488000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>/images/product-db9796b1-1760696064.jpg</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A80+</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Thức ăn bổ sung</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ĐIỀU TRỊ MYCOPLASMA SUIS, HẬU MYCOPLASMA SUIS
+PHÙ HỢP CHO HEO NÁI, HEO CON, HEO THỊT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;&lt;div&gt;- Oxytetracycline ..................................... 500 g&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ ................................. 1000 g&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;- Gia cầm: Đặc trị CRD, CCRD, hen khẹc, khò khè, sưng phù đầu, viêm phổi, viêm khớp, viêm ruột, tiêu chảy do E.coli, tụ huyết trùng, viêm buồng trứng ở gà đẻ&lt;/div&gt;&lt;div&gt;- Gia súc: Trị bệnh viêm phổi, viêm phổi màng phổi, suyễn lợn, viêm teo mũi, các chứng rối loạn tiêu hóa, hồng lị, tiêu chảy do E.coli, Lepto, liên cầu khuẩn,...&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CHỈ ĐỊNH CỦA BSTY:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;Điều trị Mycoplasma suis, duy trì liên tục 5 - 10 ngày giúp dứt điểm mycoplasma suis.&lt;/div&gt;&lt;div&gt;Thích hợp cho heo nái, heo con, heo thịt.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;Hòa nước uống hoặc trộn thức ăn.&lt;/div&gt;&lt;div&gt;Gia cầm: 1g/ 6 - 8 lít nước hoặc 1g/ 30 - 35kg thể trọng/ ngày.&lt;/div&gt;&lt;div&gt;Gia súc, heo: 1g/40 - 50 kg thể trọng/ ngày.&lt;/div&gt;&lt;div&gt;Dùng liên tục trong 3 - 5 ngày.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;8 ngày.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>685000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>685000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>/images/product-a6d57248-1760696246.jpg</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SIÊU BỔ GAN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Thức ăn bổ sung</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TĂNG CƯỜNG CHỨC NĂNG GAN, BỔ GAN LỢI MẬT
+TĂNG CƯỜNG CHUYỂN HÓA, TRAO ĐỔI CHẤT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;&lt;div&gt;- Sorbitol*(min) ............................ 300.000 mg&lt;/div&gt;&lt;div&gt;- L – lysine (min).................................. 3000 mg&lt;/div&gt;&lt;div&gt;- DL - DL - Methionine min* (min)...... 800 mg&lt;/div&gt;&lt;div&gt;- Thiamin*(min).................................... 1000 mg&lt;/div&gt;&lt;div&gt;- Inositol*(min)..................................... 1000 mg&lt;/div&gt;&lt;div&gt;- Kẽm (Zn) (min - max) ......... 1500 - 3000 mg&lt;/div&gt;&lt;div&gt;- Potassium (Kali) (min - max)......... 5,000 mg&lt;/div&gt;&lt;div&gt;- Chất mang vừa đủ ........................... 1,000 g&lt;/div&gt;&lt;div&gt;Sản phẩm không chứa kháng sinh, hoocmon.&lt;/div&gt;&lt;div&gt;Bổ sung thảo dược astiso, betain, acid amin tổng hợp và vitamin tổng hợp.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;- Bổ sung các axit amin và vitamin cần thiết và các dưỡng chất quan trọng, giúp vật nuôi sinh trưởng và phát triển khỏe mạnh.&lt;/div&gt;&lt;div&gt;- Giải độc nhanh, phục hồi chức năng gan, tái tạo tế bào gan, ngăn ngừa các bệnh về gan như vàng gan, sưng gan, đỏ gan, teo gan.&lt;/div&gt;&lt;div&gt;- Tăng cường sức đề kháng, tăng cường miễn dịch, hạn chế bệnh kế phát.&lt;/div&gt;&lt;div&gt;- Phòng chống stress do ngoại cảnh, chủng ngừa vaccine, vận chuyển, tách đàn… hỗ trợ hiệu quả trong phòng bệnh thường gặp như: Gumboro, CRD trên gia cầm, tiêu chảy…&lt;/div&gt;&lt;div&gt;- Cải thiện FCR. Vật nuôi lớn nhanh, khỏe mạnh, ít bệnh. Góp phần giảm thiểu ô nhiễm môi trường nuôi.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;CÁCH DÙNG:&lt;/div&gt;&lt;div&gt;Hòa nước uống hoặc trộn với thức ăn.&lt;/div&gt;&lt;div&gt;LIỀU DÙNG:&amp;nbsp;&lt;/div&gt;&lt;div&gt;Gia súc: 1g/4-5 lít nước hoặc 20 - 25kg thể trọng.&lt;/div&gt;&lt;div&gt;Gia cầm: 1g/3-4 lít nước hoặc 15 - 20kg thể trọng.&lt;/div&gt;&lt;div&gt;Trường hợp vật nuôi mệt mỏi hoặc cần giải độc cấp, cần thiết có thể sử dụng liều lượng gấp đôi.&lt;/div&gt;&lt;div&gt;Nên sử dụng thường xuyên trong suôt vụ nuôi để bảo vệ gan, kích thích miễn dịch và tăng cường tiêu hóa.&lt;/div&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>280000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>280000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>/images/product-3f2f0dc5-1760696514.jpg</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>37</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SIÊU ĐẠM BÉO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Thức ăn bổ sung</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VỖ BÉO CẤP TỐC, NỞ ỨC, DÀY LƯỜN, CHẮC THỊT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;&lt;div&gt;- Amylase*(min)...................................... 2400 IU&lt;/div&gt;&lt;div&gt;- Protease*(min)..................................... 4000 IU&lt;/div&gt;&lt;div&gt;- DH – Methionin*(min).................... 20.000 mg&lt;/div&gt;&lt;div&gt;- Lysine (min)...................................... 50.000 mg&lt;/div&gt;&lt;div&gt;- Vitamin A*(min)........................... 2.000.000 IU&lt;/div&gt;&lt;div&gt;- Vitamin D*(min)........................... 1.000.000 IU&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Vitamin E*(min).................................. 2000 mg&lt;/div&gt;&lt;div&gt;- Vitamin B6........................................... 1000 mg&lt;/div&gt;&lt;div&gt;- Vitamin PP........................................... 1000 mg&lt;/div&gt;&lt;div&gt;- Vitamin C............................................. 1000 mg&lt;/div&gt;&lt;div&gt;- Đạm tổng số............................................. 150 g&lt;/div&gt;&lt;div&gt;- Chất mang vừa đủ .............................. 1000 g&lt;/div&gt;&lt;div&gt;Sản phẩm không chứa kháng sinh, hoocmon&lt;/div&gt;&lt;div&gt;Bổ sung hỗn hợp 10 loại enzyme hữu hiệu: Phytase, amyase, xylanase, protatease, mannanase, cellulose, pectinase, B-Glucanase, a-Galactosidase, lipase.)&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;- Nở ức - dày lườn - chắc thịt. Không hăng, không sung hạn chế tối đa cắn mổ trong giai đoạn sử dụng sản phẩm.&lt;/div&gt;&lt;div&gt;- Công thức dinh dưỡng hoàn chỉnh, hàm lượng đạm cao, hiệu quả vỗ béo nhanh, xuất chuồng sớm, hạn chế dùng kháng sinh trong chăn nuôi gia súc gia cầm.&lt;/div&gt;&lt;div&gt;- Giải pháp nâng cao hiệu quả chăn nuôi. Bổ sung vitamin, acid amin và enzyme cho vật nuôi trong các trường hợp cần thiết.&lt;/div&gt;&lt;div&gt;- Kích thích tính thèm ăn và tăng cường tiêu hóa, hấp thu, cải thiện hiệu quả thức ăn.&lt;/div&gt;&lt;div&gt;- Giảm tỷ lệ chết, tăng cường sức đề kháng, tăng cường khả năng miễn dịch cho vật nuôi.&lt;/div&gt;&lt;div&gt;- Giảm tiêu tốn thức ăn, rút ngắn thời gian nuôi.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;Hòa nước uống hoặc trộn với thức ăn.&lt;/div&gt;&lt;div&gt;Gia cầm: 1g/3-4 lít nước uống hoặc 15-20kg thể trọng&amp;nbsp;&lt;/div&gt;&lt;div&gt;Gia súc: 1g/6-8lit nước uống hoặc 30-40kg thể trọng&lt;/div&gt;&lt;div&gt;Trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.&lt;/div&gt;&lt;div&gt;Lưu ý: nên dùng kết với với sản phẩm ĐỎ TÍCH KÍCH MÀO để đạt hiệu quả cao nhất.&lt;/div&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>448000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>448000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>/images/product-85151e1c-1760696681.jpg</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ĐỎ TÍCH KÍCH MÀO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vitamin &amp; khoáng chất</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TĂNG CHUYỂN HÓA, HẤP THỤ, NGON MIỆNG ĂN KHỎE
+ĐỎ TÍCH KÍCH MÀO, BẬT CỰA, DA VÀNG, LÔNG MƯỢT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;&lt;div&gt;- Lysine* (Min).................................... 20.000 mg&amp;nbsp;&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Selen (Min – max)........................... 5 - 100 mg&lt;/div&gt;&lt;div&gt;- Mg (Min – max)..................... 2000 - 3000 mg&lt;/div&gt;&lt;div&gt;- Zn (Min – max)..................... 1000 - 18000 mg&lt;/div&gt;&lt;div&gt;- Vitamin B1*(Min).................................. 1000 mg&lt;/div&gt;&lt;div&gt;- Vitamin B6*(Min)................................. 1000 mg&lt;/div&gt;&lt;div&gt;- Vitamin PP*(Min)................................ 2000 mg&lt;/div&gt;&lt;div&gt;- Vitamin B12*(Min)................................. 800 mg&lt;/div&gt;&lt;div&gt;- Vitamin D*(Min)............................... 800.000 UI&lt;/div&gt;&lt;div&gt;- Vitamin A*(Min)............................... 500.000 UI&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Vitamin E* (Min)................................... 1500 mg&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Vitamin C* (Min).................................... 100 mg&lt;/div&gt;&lt;div&gt;- Dung môi vừa đủ ….............................. 1000 ml&lt;/div&gt;&lt;div&gt;Sản phẩm không chứa kháng sinh, hoocmon&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;- Kích mào, bật mã, bóng lông, tía chân.&lt;/div&gt;&lt;div&gt;- Bổ sung tổng hợp nhiều loại vitamin thiết yếu, và acid amin cho vật nuôi trong các trường hợp thức ăn không đủ dưỡng chất, rối loạn trao đổi chất, tiêu chảy kéo dài hoặc sau khi chủng ngừa vaccine.&lt;/div&gt;&lt;div&gt;- Kích thích tính thèm ăn và tăng cường tiêu hóa, hấp thu, cải thiện hiệu quả thức ăn.&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Kích thích lông da. Kích mào đỏ, bung lông, bật cựa. Gia cầm đẹp mã, nặng cân.&lt;/div&gt;&lt;div&gt;- Kích thích sinh sản, tăng chất lượng và sản lượng trứng.&amp;nbsp;&lt;/div&gt;&lt;div&gt;- Giảm tỷ lệ chết gây ra do stress hoặc trong trường hợp mật độ chăn nuôi nhiều, tách đàn, chuyển mùa, thay đổi thức ăn…&lt;/div&gt;&lt;div&gt;- Tăng cường sức đề kháng, tăng cường khả năng miễn dịch. Vật nuôi lớn nhanh khỏe mạnh.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;Úm gia cầm: 1ml/1lít nước.&lt;/div&gt;&lt;div&gt;Gia cầm đẻ, thịt: 1ml/2-3 lit nước.&lt;/div&gt;&lt;div&gt;Gia súc: 1ml/1 lít nước hoặc 500kg thức ăn .&lt;/div&gt;&lt;div&gt;Lưu ý: Nên sử dụng thường xuyên để tăng sức đề kháng và vỗ béo cho vật nuôi, trong trường hợp cần thiết có thể sử dụng liều lượng tăng gấp đôi.&lt;/div&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>265000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>265000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>/images/product-cb9fc55e-1760696877.jpg</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>39</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WINTRIL MAX</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ĐẶC TRỊ TIÊU CHẢY, HEN KHẸC,
+SƯNG PHÙ ĐẦU, TỤ HUYẾT TRÙNG</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN:&lt;/b&gt;&lt;div&gt;Enrofloxacin (dihydrate) ................ 20 g&lt;/div&gt;&lt;div&gt;Dung môi vừa đủ ........................ 100 ml&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Trị nhiễm trùng đường tiêu hóa, hô hấp, niệu sinh dục, nhiễm trùng da và vết thương, viêm khớp trên trâu, bò, ngựa, dê, cừu, lợn, chó, mèo cụ thể: viêm ruột, tiêu chảy, chướng bụng, đầy hơi, phân trắng, phân vàng, phân xi măng, thương hàn, phó thương hàn, tụ huyết trùng, các trường hợp tiêu chảy không rõ nguyên nhân.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;LIỀU LƯỢNG VÀ CÁCH DÙNG:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Tiêm bắp theo liều:&lt;/div&gt;&lt;div&gt;+ Trên heo, dê, cừu: 1ml/15-20kg TT.&lt;/div&gt;&lt;div&gt;+ Trên trâu, bò: 1ml/30-40kg TT.&lt;/div&gt;&lt;div&gt;- Tiêm mũi duy nhất, trường hợp bệnh nặng tiêm nhắc lại sau 48h.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;THỜI GIAN NGƯNG SỬ DỤNG THUỐC:&lt;/b&gt;&lt;/div&gt;&lt;div&gt;- Lấy thịt và nội tạng: 13 ngày.&lt;/div&gt;&lt;div&gt;- Lấy sữa: 4 ngày.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>365000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>365000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>/images/product-cff919d4-1761021088.jpg</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/public/data/halife_products.xlsx
+++ b/public/data/halife_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ25"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,7 +722,7 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="b">
         <v>0</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>550000</v>
+        <v>650000</v>
       </c>
       <c r="J11" t="n">
-        <v>550000</v>
+        <v>650000</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3036,10 +3036,10 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>228000</v>
+        <v>225000</v>
       </c>
       <c r="J18" t="n">
-        <v>228000</v>
+        <v>225000</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3250,10 +3250,10 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>488000</v>
+        <v>485000</v>
       </c>
       <c r="J20" t="n">
-        <v>488000</v>
+        <v>485000</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3857,6 +3857,227 @@
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>40</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PRO MEN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Vitamin &amp; khoáng chất</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BỔ SUNG SACCHAROMYCES
+THAN HOẠT TÍNH, TÁ DƯỢC ĐỘC QUYỀN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;THÀNH PHẦN&lt;/b&gt;&lt;div&gt;&lt;div style=""&gt;Trong 1000g có chứa:&lt;/div&gt;&lt;div style=""&gt;Bacillus Subtillis (min)......................................1x108 CFU&lt;/div&gt;&lt;div style=""&gt;Bacillus Cereus (min)........................................1x108 CFU&lt;/div&gt;&lt;div style=""&gt;Thành phần bổ sung Saccharomyces, than hoạt tính, tá dược độc quyền vừa đủ.........................1000 g&lt;/div&gt;&lt;/div&gt;&lt;div style=""&gt;Sản phẩm không chứa kháng sinh, hoocmon và các chất độc hại&lt;/div&gt;&lt;div style=""&gt;&lt;br&gt;&lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;CÁCH DÙNG VÀ LIỀU LƯỢNG&lt;/b&gt;&lt;/div&gt;&lt;div style=""&gt;&lt;div&gt;Trộn vào thức ăn hoặc pha nước uống.&lt;/div&gt;&lt;div&gt;Gia cầm: 1gr/ 10-20kg thể trọng.&lt;/div&gt;&lt;div&gt;Gia súc: 1gr/ 30-40kg thể trọng.&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;CÔNG DỤNG&lt;/b&gt;&lt;/div&gt;&lt;div&gt;&lt;div&gt;- Bổ sung men vi sinh giúp gia súc, gia cầm ổn định, cân bằng hệ vi sinh vật đường ruột, hấp thu thức ăn triệt để, cải thiện FCR.&lt;/div&gt;&lt;div&gt;- Ngừa bệnh E.coli, thương hàn, viêm ruột hoại tử trên gà, vịt, ngan, cút.&lt;/div&gt;&lt;div&gt;- Phòng và xử lý các bệnh thường gặp trên gia súc gia cầm như: Bệnh phân trắng lợn con trong giai đoạn theo mẹ, bệnh xưng phù đầu của lợn con, bệnh phân sống do dối loạn tiêu hóa.&lt;/div&gt;&lt;div&gt;- Chống rối loạn tiêu hóa do sử dụng kháng sinh trên gia súc, gia cầm.&lt;/div&gt;&lt;/div&gt;&lt;div&gt;&lt;br&gt;&lt;/div&gt;&lt;div&gt;&lt;b&gt;BẢO QUẢN&lt;/b&gt;&lt;/div&gt;&lt;div&gt;Nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp, nhiệt độ không quá 30°C.&lt;/div&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>350000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>/images/product-2605bb2c-1766128705.jpg</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>41</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BEST KILL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thuốc kháng sinh</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sát trung thế hệ mới, diệt khuẩn mạnh, diệt sạch viruss, vi khuẩn gây bệnh</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sát trung thế hệ mới, diệt khuẩn mạnh, diệt sạch viruss, vi khuẩn gây bệnh</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>265000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>265000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hộp</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>24 tháng</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>HALIFE Việt Nhật</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>/images/product-15c9e7a9-1769843742.jpg</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>/images/product-2d87de8a-1769843846.jpg;/images/product-6811a9a9-1769843852.jpg</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>active</t>
         </is>
